--- a/воры/Amazing_Pics_SKU ALL.xlsx
+++ b/воры/Amazing_Pics_SKU ALL.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\воры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EFFAFF-FA59-4205-96AF-35946BEDE0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8929A91-5567-49C0-A11A-21AE5EAA0EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="426">
   <si>
     <t>Артикул</t>
   </si>
@@ -1297,6 +1297,12 @@
   </si>
   <si>
     <t>C:\Users\Max\Documents\GitHub\Ozon_upload\Tatulya\photoshop cards\wb_export_A4_bundle_screenshot.psd</t>
+  </si>
+  <si>
+    <t>вор14</t>
+  </si>
+  <si>
+    <t>вор15</t>
   </si>
 </sst>
 </file>
@@ -1436,7 +1442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1460,6 +1466,7 @@
     </xf>
     <xf numFmtId="1" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1724,17 +1731,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X408"/>
+  <dimension ref="A1:Z408"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.140625" style="3" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" style="16" customWidth="1"/>
-    <col min="3" max="15" width="11" style="3" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="8.7109375" style="3"/>
+    <col min="3" max="17" width="11" style="3" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1780,11 +1787,17 @@
       <c r="O1" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -1798,33 +1811,33 @@
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
-      <c r="P2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="15">
         <v>1506320059</v>
       </c>
-      <c r="P3" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R3" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="15">
         <v>1506318673</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="R4" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
@@ -1834,11 +1847,11 @@
       <c r="C5" s="3">
         <v>3795487621</v>
       </c>
-      <c r="P5" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R5" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -1866,22 +1879,22 @@
       <c r="I6" s="3">
         <v>2873299815</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="R6" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="15">
         <v>1506332556</v>
       </c>
-      <c r="P7" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R7" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
@@ -1912,11 +1925,11 @@
       <c r="J8" s="3">
         <v>2873298399</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="R8" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
@@ -1947,11 +1960,11 @@
       <c r="J9" s="3">
         <v>2873297490</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="R9" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>21</v>
       </c>
@@ -1964,11 +1977,11 @@
       <c r="D10" s="3">
         <v>3795490298</v>
       </c>
-      <c r="P10" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R10" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
@@ -1993,11 +2006,11 @@
       <c r="H11" s="3">
         <v>2873299998</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="R11" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>23</v>
       </c>
@@ -2013,11 +2026,11 @@
       <c r="E12" s="3">
         <v>4561090350</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="R12" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>24</v>
       </c>
@@ -2048,11 +2061,11 @@
       <c r="J13" s="3">
         <v>2873299396</v>
       </c>
-      <c r="P13" s="9" t="s">
+      <c r="R13" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>25</v>
       </c>
@@ -2080,11 +2093,11 @@
       <c r="I14" s="3">
         <v>2873297962</v>
       </c>
-      <c r="P14" s="9" t="s">
+      <c r="R14" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
@@ -2112,11 +2125,11 @@
       <c r="I15" s="3">
         <v>2873299595</v>
       </c>
-      <c r="P15" s="7" t="s">
+      <c r="R15" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
@@ -2138,11 +2151,11 @@
       <c r="G16" s="3">
         <v>4724082788</v>
       </c>
-      <c r="P16" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R16" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -2176,11 +2189,11 @@
       <c r="K17" s="3">
         <v>4561104825</v>
       </c>
-      <c r="P17" s="9" t="s">
+      <c r="R17" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -2205,11 +2218,11 @@
       <c r="H18" s="3">
         <v>2873303150</v>
       </c>
-      <c r="P18" s="7" t="s">
+      <c r="R18" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -2234,11 +2247,11 @@
       <c r="H19" s="3">
         <v>2873298127</v>
       </c>
-      <c r="P19" s="7" t="s">
+      <c r="R19" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -2251,11 +2264,11 @@
       <c r="D20" s="3">
         <v>3795490229</v>
       </c>
-      <c r="P20" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R20" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -2280,22 +2293,22 @@
       <c r="H21" s="3">
         <v>2873298690</v>
       </c>
-      <c r="P21" s="7" t="s">
+      <c r="R21" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="15">
         <v>1506332524</v>
       </c>
-      <c r="P22" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R22" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>34</v>
       </c>
@@ -2311,11 +2324,11 @@
       <c r="E23" s="3">
         <v>3795492087</v>
       </c>
-      <c r="P23" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R23" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>35</v>
       </c>
@@ -2331,11 +2344,11 @@
       <c r="E24" s="3">
         <v>3795492175</v>
       </c>
-      <c r="P24" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R24" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>36</v>
       </c>
@@ -2360,11 +2373,11 @@
       <c r="H25" s="3">
         <v>2873306693</v>
       </c>
-      <c r="P25" s="7" t="s">
+      <c r="R25" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>37</v>
       </c>
@@ -2392,11 +2405,11 @@
       <c r="I26" s="3">
         <v>4561108893</v>
       </c>
-      <c r="P26" s="9" t="s">
+      <c r="R26" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>38</v>
       </c>
@@ -2409,11 +2422,11 @@
       <c r="D27" s="3">
         <v>3795488058</v>
       </c>
-      <c r="P27" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R27" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>39</v>
       </c>
@@ -2441,11 +2454,11 @@
       <c r="I28" s="3">
         <v>2873303477</v>
       </c>
-      <c r="P28" s="7" t="s">
+      <c r="R28" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>40</v>
       </c>
@@ -2479,11 +2492,11 @@
       <c r="K29" s="3">
         <v>4561093970</v>
       </c>
-      <c r="P29" s="7" t="s">
+      <c r="R29" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>41</v>
       </c>
@@ -2511,22 +2524,22 @@
       <c r="I30" s="3">
         <v>2873305812</v>
       </c>
-      <c r="P30" s="7" t="s">
+      <c r="R30" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B31" s="15">
         <v>1506331474</v>
       </c>
-      <c r="P31" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R31" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>43</v>
       </c>
@@ -2560,11 +2573,11 @@
       <c r="K32" s="3">
         <v>2873303922</v>
       </c>
-      <c r="P32" s="7" t="s">
+      <c r="R32" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>44</v>
       </c>
@@ -2595,11 +2608,11 @@
       <c r="J33" s="3">
         <v>2873299413</v>
       </c>
-      <c r="P33" s="7" t="s">
+      <c r="R33" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>45</v>
       </c>
@@ -2630,11 +2643,11 @@
       <c r="J34" s="3">
         <v>2873298887</v>
       </c>
-      <c r="P34" s="9" t="s">
+      <c r="R34" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>46</v>
       </c>
@@ -2665,11 +2678,11 @@
       <c r="J35" s="3">
         <v>2873299683</v>
       </c>
-      <c r="P35" s="9" t="s">
+      <c r="R35" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>47</v>
       </c>
@@ -2697,11 +2710,11 @@
       <c r="I36" s="3">
         <v>2873299189</v>
       </c>
-      <c r="P36" s="7" t="s">
+      <c r="R36" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>48</v>
       </c>
@@ -2714,11 +2727,11 @@
       <c r="D37" s="3">
         <v>4723913759</v>
       </c>
-      <c r="P37" s="7" t="s">
+      <c r="R37" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>49</v>
       </c>
@@ -2746,11 +2759,11 @@
       <c r="I38" s="3">
         <v>2873298948</v>
       </c>
-      <c r="P38" s="9" t="s">
+      <c r="R38" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>50</v>
       </c>
@@ -2778,11 +2791,11 @@
       <c r="I39" s="3">
         <v>2873298400</v>
       </c>
-      <c r="P39" s="7" t="s">
+      <c r="R39" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>51</v>
       </c>
@@ -2813,11 +2826,11 @@
       <c r="J40" s="3">
         <v>4561086043</v>
       </c>
-      <c r="P40" s="7" t="s">
+      <c r="R40" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>52</v>
       </c>
@@ -2860,11 +2873,11 @@
       <c r="N41" s="3">
         <v>2873303103</v>
       </c>
-      <c r="P41" s="7" t="s">
+      <c r="R41" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>53</v>
       </c>
@@ -2877,11 +2890,11 @@
       <c r="D42" s="3">
         <v>3939769350</v>
       </c>
-      <c r="P42" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R42" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>54</v>
       </c>
@@ -2909,11 +2922,11 @@
       <c r="I43" s="3">
         <v>4561091143</v>
       </c>
-      <c r="P43" s="7" t="s">
+      <c r="R43" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>55</v>
       </c>
@@ -2932,11 +2945,11 @@
       <c r="F44" s="3">
         <v>2898637721</v>
       </c>
-      <c r="P44" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R44" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>56</v>
       </c>
@@ -2958,11 +2971,11 @@
       <c r="G45" s="3">
         <v>4544787512</v>
       </c>
-      <c r="P45" s="7" t="s">
+      <c r="R45" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>57</v>
       </c>
@@ -2981,11 +2994,11 @@
       <c r="F46" s="3">
         <v>3939771058</v>
       </c>
-      <c r="P46" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R46" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>58</v>
       </c>
@@ -3019,11 +3032,11 @@
       <c r="K47" s="3">
         <v>2873298381</v>
       </c>
-      <c r="P47" s="7" t="s">
+      <c r="R47" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>59</v>
       </c>
@@ -3051,11 +3064,11 @@
       <c r="I48" s="3">
         <v>2873305358</v>
       </c>
-      <c r="P48" s="7" t="s">
+      <c r="R48" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>60</v>
       </c>
@@ -3083,11 +3096,11 @@
       <c r="I49" s="3">
         <v>2873302064</v>
       </c>
-      <c r="P49" s="7" t="s">
+      <c r="R49" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>61</v>
       </c>
@@ -3106,11 +3119,11 @@
       <c r="F50" s="3">
         <v>4724082672</v>
       </c>
-      <c r="P50" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R50" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>62</v>
       </c>
@@ -3141,11 +3154,11 @@
       <c r="J51" s="3">
         <v>4561091170</v>
       </c>
-      <c r="P51" s="9" t="s">
+      <c r="R51" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>63</v>
       </c>
@@ -3158,11 +3171,11 @@
       <c r="D52" s="3">
         <v>4561107576</v>
       </c>
-      <c r="P52" s="9" t="s">
+      <c r="R52" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>64</v>
       </c>
@@ -3172,11 +3185,11 @@
       <c r="C53" s="3">
         <v>3939771024</v>
       </c>
-      <c r="P53" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R53" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>65</v>
       </c>
@@ -3207,11 +3220,11 @@
       <c r="J54" s="3">
         <v>2873299691</v>
       </c>
-      <c r="P54" s="7" t="s">
+      <c r="R54" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>66</v>
       </c>
@@ -3242,11 +3255,11 @@
       <c r="J55" s="3">
         <v>2873297952</v>
       </c>
-      <c r="P55" s="9" t="s">
+      <c r="R55" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>67</v>
       </c>
@@ -3280,11 +3293,11 @@
       <c r="K56" s="3">
         <v>4561101994</v>
       </c>
-      <c r="P56" s="9" t="s">
+      <c r="R56" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>68</v>
       </c>
@@ -3309,11 +3322,11 @@
       <c r="H57" s="3">
         <v>4561101622</v>
       </c>
-      <c r="P57" s="9" t="s">
+      <c r="R57" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>69</v>
       </c>
@@ -3326,11 +3339,11 @@
       <c r="D58" s="3">
         <v>3135875161</v>
       </c>
-      <c r="P58" s="7" t="s">
+      <c r="R58" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>70</v>
       </c>
@@ -3358,11 +3371,11 @@
       <c r="I59" s="3">
         <v>2873298950</v>
       </c>
-      <c r="P59" s="7" t="s">
+      <c r="R59" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>71</v>
       </c>
@@ -3393,11 +3406,11 @@
       <c r="J60" s="3">
         <v>2873298258</v>
       </c>
-      <c r="P60" s="9" t="s">
+      <c r="R60" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>72</v>
       </c>
@@ -3431,11 +3444,11 @@
       <c r="K61" s="3">
         <v>2873298548</v>
       </c>
-      <c r="P61" s="9" t="s">
+      <c r="R61" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>73</v>
       </c>
@@ -3448,11 +3461,11 @@
       <c r="D62" s="3">
         <v>3795490035</v>
       </c>
-      <c r="P62" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R62" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>74</v>
       </c>
@@ -3462,11 +3475,11 @@
       <c r="C63" s="3">
         <v>3678859195</v>
       </c>
-      <c r="P63" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R63" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>75</v>
       </c>
@@ -3497,11 +3510,11 @@
       <c r="J64" s="3">
         <v>2873299334</v>
       </c>
-      <c r="P64" s="9" t="s">
+      <c r="R64" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>76</v>
       </c>
@@ -3520,11 +3533,11 @@
       <c r="F65" s="3">
         <v>3795491581</v>
       </c>
-      <c r="P65" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R65" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>77</v>
       </c>
@@ -3537,11 +3550,11 @@
       <c r="D66" s="3">
         <v>3939760105</v>
       </c>
-      <c r="P66" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R66" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>78</v>
       </c>
@@ -3560,11 +3573,11 @@
       <c r="F67" s="3">
         <v>3678858448</v>
       </c>
-      <c r="P67" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R67" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>79</v>
       </c>
@@ -3577,11 +3590,11 @@
       <c r="D68" s="3">
         <v>3939763988</v>
       </c>
-      <c r="P68" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R68" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>80</v>
       </c>
@@ -3597,11 +3610,11 @@
       <c r="E69" s="3">
         <v>3795489195</v>
       </c>
-      <c r="P69" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R69" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>81</v>
       </c>
@@ -3614,11 +3627,11 @@
       <c r="D70" s="3">
         <v>3795487618</v>
       </c>
-      <c r="P70" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R70" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>82</v>
       </c>
@@ -3643,11 +3656,11 @@
       <c r="H71" s="3">
         <v>4724084510</v>
       </c>
-      <c r="P71" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R71" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>83</v>
       </c>
@@ -3663,11 +3676,11 @@
       <c r="E72" s="3">
         <v>3795492355</v>
       </c>
-      <c r="P72" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R72" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>84</v>
       </c>
@@ -3686,11 +3699,11 @@
       <c r="F73" s="3">
         <v>4724088385</v>
       </c>
-      <c r="P73" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R73" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>85</v>
       </c>
@@ -3712,11 +3725,11 @@
       <c r="G74" s="3">
         <v>3678856208</v>
       </c>
-      <c r="P74" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R74" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>86</v>
       </c>
@@ -3729,11 +3742,11 @@
       <c r="D75" s="3">
         <v>3939765957</v>
       </c>
-      <c r="P75" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R75" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>87</v>
       </c>
@@ -3749,22 +3762,22 @@
       <c r="E76" s="3">
         <v>3939763800</v>
       </c>
-      <c r="P76" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R76" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B77" s="15">
         <v>1522019450</v>
       </c>
-      <c r="P77" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R77" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>89</v>
       </c>
@@ -3780,11 +3793,11 @@
       <c r="E78" s="3">
         <v>4724083630</v>
       </c>
-      <c r="P78" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R78" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>90</v>
       </c>
@@ -3803,11 +3816,11 @@
       <c r="F79" s="3">
         <v>4420198779</v>
       </c>
-      <c r="P79" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R79" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>91</v>
       </c>
@@ -3820,11 +3833,11 @@
       <c r="D80" s="3">
         <v>3678857437</v>
       </c>
-      <c r="P80" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R80" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>92</v>
       </c>
@@ -3846,11 +3859,11 @@
       <c r="G81" s="3">
         <v>3678858225</v>
       </c>
-      <c r="P81" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R81" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>93</v>
       </c>
@@ -3875,11 +3888,11 @@
       <c r="H82" s="3">
         <v>4724083351</v>
       </c>
-      <c r="P82" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R82" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>94</v>
       </c>
@@ -3901,11 +3914,11 @@
       <c r="G83" s="3">
         <v>3678868875</v>
       </c>
-      <c r="P83" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R83" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>95</v>
       </c>
@@ -3927,11 +3940,11 @@
       <c r="G84" s="3">
         <v>3678869173</v>
       </c>
-      <c r="P84" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R84" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>96</v>
       </c>
@@ -3956,11 +3969,11 @@
       <c r="H85" s="3">
         <v>4724083134</v>
       </c>
-      <c r="P85" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R85" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>97</v>
       </c>
@@ -3982,11 +3995,11 @@
       <c r="G86" s="3">
         <v>3678867222</v>
       </c>
-      <c r="P86" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R86" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>98</v>
       </c>
@@ -4011,11 +4024,11 @@
       <c r="H87" s="3">
         <v>4724084366</v>
       </c>
-      <c r="P87" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R87" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>99</v>
       </c>
@@ -4031,11 +4044,11 @@
       <c r="E88" s="3">
         <v>3795489593</v>
       </c>
-      <c r="P88" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R88" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>100</v>
       </c>
@@ -4063,11 +4076,11 @@
       <c r="I89" s="3">
         <v>4513707779</v>
       </c>
-      <c r="P89" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R89" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>101</v>
       </c>
@@ -4089,11 +4102,11 @@
       <c r="G90" s="3">
         <v>3678869285</v>
       </c>
-      <c r="P90" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R90" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>102</v>
       </c>
@@ -4112,11 +4125,11 @@
       <c r="F91" s="3">
         <v>3795488259</v>
       </c>
-      <c r="P91" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R91" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>103</v>
       </c>
@@ -4132,11 +4145,11 @@
       <c r="E92" s="3">
         <v>3678870845</v>
       </c>
-      <c r="P92" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R92" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>104</v>
       </c>
@@ -4158,11 +4171,11 @@
       <c r="G93" s="3">
         <v>3678867757</v>
       </c>
-      <c r="P93" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R93" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>105</v>
       </c>
@@ -4178,11 +4191,11 @@
       <c r="E94" s="3">
         <v>3795491892</v>
       </c>
-      <c r="P94" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R94" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>106</v>
       </c>
@@ -4198,11 +4211,11 @@
       <c r="E95" s="3">
         <v>3795491512</v>
       </c>
-      <c r="P95" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R95" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>107</v>
       </c>
@@ -4212,11 +4225,11 @@
       <c r="C96" s="3">
         <v>3795489222</v>
       </c>
-      <c r="P96" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R96" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>108</v>
       </c>
@@ -4232,11 +4245,11 @@
       <c r="E97" s="3">
         <v>3678868658</v>
       </c>
-      <c r="P97" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R97" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>109</v>
       </c>
@@ -4255,11 +4268,11 @@
       <c r="F98" s="3">
         <v>3678859650</v>
       </c>
-      <c r="P98" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R98" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>110</v>
       </c>
@@ -4275,11 +4288,11 @@
       <c r="E99" s="3">
         <v>4724087690</v>
       </c>
-      <c r="P99" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R99" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>111</v>
       </c>
@@ -4301,11 +4314,11 @@
       <c r="G100" s="3">
         <v>4724084275</v>
       </c>
-      <c r="P100" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R100" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>112</v>
       </c>
@@ -4324,11 +4337,11 @@
       <c r="F101" s="3">
         <v>3678867391</v>
       </c>
-      <c r="P101" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R101" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>113</v>
       </c>
@@ -4344,11 +4357,11 @@
       <c r="E102" s="3">
         <v>3678869127</v>
       </c>
-      <c r="P102" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R102" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>114</v>
       </c>
@@ -4367,11 +4380,11 @@
       <c r="F103" s="3">
         <v>4724084231</v>
       </c>
-      <c r="P103" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R103" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>115</v>
       </c>
@@ -4393,11 +4406,11 @@
       <c r="G104" s="3">
         <v>3678860029</v>
       </c>
-      <c r="P104" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R104" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>116</v>
       </c>
@@ -4410,11 +4423,11 @@
       <c r="D105" s="3">
         <v>4753796086</v>
       </c>
-      <c r="P105" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R105" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>117</v>
       </c>
@@ -4445,11 +4458,11 @@
       <c r="J106" s="3">
         <v>2873304879</v>
       </c>
-      <c r="P106" s="9" t="s">
+      <c r="R106" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>118</v>
       </c>
@@ -4468,22 +4481,22 @@
       <c r="F107" s="3">
         <v>3939773240</v>
       </c>
-      <c r="P107" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R107" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>119</v>
       </c>
       <c r="B108" s="15">
         <v>1532940236</v>
       </c>
-      <c r="P108" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R108" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>120</v>
       </c>
@@ -4505,11 +4518,11 @@
       <c r="G109" s="3">
         <v>3678867940</v>
       </c>
-      <c r="P109" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R109" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>121</v>
       </c>
@@ -4537,11 +4550,11 @@
       <c r="I110" s="3">
         <v>2873297756</v>
       </c>
-      <c r="P110" s="7" t="s">
+      <c r="R110" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>122</v>
       </c>
@@ -4569,11 +4582,11 @@
       <c r="I111" s="3">
         <v>2873298550</v>
       </c>
-      <c r="P111" s="7" t="s">
+      <c r="R111" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>123</v>
       </c>
@@ -4601,22 +4614,22 @@
       <c r="I112" s="3">
         <v>2873298641</v>
       </c>
-      <c r="P112" s="7" t="s">
+      <c r="R112" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>124</v>
       </c>
       <c r="B113" s="15">
         <v>1532936774</v>
       </c>
-      <c r="P113" s="7" t="s">
+      <c r="R113" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>125</v>
       </c>
@@ -4647,11 +4660,11 @@
       <c r="J114" s="3">
         <v>2873297833</v>
       </c>
-      <c r="P114" s="9" t="s">
+      <c r="R114" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>126</v>
       </c>
@@ -4682,44 +4695,44 @@
       <c r="J115" s="3">
         <v>2873303946</v>
       </c>
-      <c r="P115" s="9" t="s">
+      <c r="R115" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>127</v>
       </c>
       <c r="B116" s="15">
         <v>1532937063</v>
       </c>
-      <c r="P116" s="9" t="s">
+      <c r="R116" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>128</v>
       </c>
       <c r="B117" s="15">
         <v>1532937026</v>
       </c>
-      <c r="P117" s="9" t="s">
+      <c r="R117" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>129</v>
       </c>
       <c r="B118" s="15">
         <v>1532940241</v>
       </c>
-      <c r="P118" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R118" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>130</v>
       </c>
@@ -4732,11 +4745,11 @@
       <c r="D119" s="3">
         <v>4723915385</v>
       </c>
-      <c r="P119" s="9" t="s">
+      <c r="R119" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>131</v>
       </c>
@@ -4773,11 +4786,11 @@
       <c r="L120" s="3">
         <v>4561079268</v>
       </c>
-      <c r="P120" s="9" t="s">
+      <c r="R120" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="121" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>132</v>
       </c>
@@ -4808,11 +4821,11 @@
       <c r="J121" s="3">
         <v>2873299160</v>
       </c>
-      <c r="P121" s="9" t="s">
+      <c r="R121" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>133</v>
       </c>
@@ -4828,11 +4841,11 @@
       <c r="E122" s="3">
         <v>3939765055</v>
       </c>
-      <c r="P122" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R122" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>134</v>
       </c>
@@ -4863,11 +4876,11 @@
       <c r="J123" s="3">
         <v>2873298743</v>
       </c>
-      <c r="P123" s="7" t="s">
+      <c r="R123" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>135</v>
       </c>
@@ -4883,22 +4896,22 @@
       <c r="E124" s="3">
         <v>4724084538</v>
       </c>
-      <c r="P124" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R124" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>136</v>
       </c>
       <c r="B125" s="15">
         <v>1532938438</v>
       </c>
-      <c r="P125" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R125" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>137</v>
       </c>
@@ -4911,11 +4924,11 @@
       <c r="D126" s="3">
         <v>3939771934</v>
       </c>
-      <c r="P126" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R126" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>138</v>
       </c>
@@ -4931,11 +4944,11 @@
       <c r="E127" s="3">
         <v>3795491665</v>
       </c>
-      <c r="P127" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R127" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>139</v>
       </c>
@@ -4948,11 +4961,11 @@
       <c r="D128" s="3">
         <v>3939770708</v>
       </c>
-      <c r="P128" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R128" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>140</v>
       </c>
@@ -4983,11 +4996,11 @@
       <c r="J129" s="3">
         <v>2873298244</v>
       </c>
-      <c r="P129" s="9" t="s">
+      <c r="R129" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>141</v>
       </c>
@@ -5009,11 +5022,11 @@
       <c r="G130" s="3">
         <v>4724084174</v>
       </c>
-      <c r="P130" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R130" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>142</v>
       </c>
@@ -5044,33 +5057,33 @@
       <c r="J131" s="3">
         <v>2873298342</v>
       </c>
-      <c r="P131" s="7" t="s">
+      <c r="R131" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>143</v>
       </c>
       <c r="B132" s="15">
         <v>1532938598</v>
       </c>
-      <c r="P132" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R132" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>144</v>
       </c>
       <c r="B133" s="15">
         <v>1532936617</v>
       </c>
-      <c r="P133" s="9" t="s">
+      <c r="R133" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>145</v>
       </c>
@@ -5101,33 +5114,33 @@
       <c r="J134" s="3">
         <v>4466038283</v>
       </c>
-      <c r="P134" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R134" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>146</v>
       </c>
       <c r="B135" s="15">
         <v>1532936541</v>
       </c>
-      <c r="P135" s="9" t="s">
+      <c r="R135" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>147</v>
       </c>
       <c r="B136" s="15">
         <v>1532936901</v>
       </c>
-      <c r="P136" s="9" t="s">
+      <c r="R136" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>148</v>
       </c>
@@ -5158,11 +5171,11 @@
       <c r="J137" s="3">
         <v>4466037381</v>
       </c>
-      <c r="P137" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R137" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>149</v>
       </c>
@@ -5193,11 +5206,11 @@
       <c r="J138" s="3">
         <v>2873298992</v>
       </c>
-      <c r="P138" s="9" t="s">
+      <c r="R138" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="139" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>150</v>
       </c>
@@ -5225,11 +5238,11 @@
       <c r="I139" s="3">
         <v>2873298693</v>
       </c>
-      <c r="P139" s="9" t="s">
+      <c r="R139" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="140" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>151</v>
       </c>
@@ -5242,11 +5255,11 @@
       <c r="D140" s="3">
         <v>4723912898</v>
       </c>
-      <c r="P140" s="7" t="s">
+      <c r="R140" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>152</v>
       </c>
@@ -5259,11 +5272,11 @@
       <c r="D141" s="3">
         <v>4561099873</v>
       </c>
-      <c r="P141" s="7" t="s">
+      <c r="R141" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>153</v>
       </c>
@@ -5294,11 +5307,11 @@
       <c r="J142" s="3">
         <v>2873298500</v>
       </c>
-      <c r="P142" s="9" t="s">
+      <c r="R142" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>154</v>
       </c>
@@ -5329,11 +5342,11 @@
       <c r="J143" s="3">
         <v>2873298834</v>
       </c>
-      <c r="P143" s="9" t="s">
+      <c r="R143" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>155</v>
       </c>
@@ -5367,11 +5380,11 @@
       <c r="K144" s="3">
         <v>2873306046</v>
       </c>
-      <c r="P144" s="7" t="s">
+      <c r="R144" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="145" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>156</v>
       </c>
@@ -5393,11 +5406,11 @@
       <c r="G145" s="3">
         <v>3116751442</v>
       </c>
-      <c r="P145" s="7" t="s">
+      <c r="R145" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>157</v>
       </c>
@@ -5437,11 +5450,11 @@
       <c r="M146" s="3">
         <v>4530261632</v>
       </c>
-      <c r="P146" s="7" t="s">
+      <c r="R146" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="147" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>158</v>
       </c>
@@ -5478,11 +5491,11 @@
       <c r="L147" s="3">
         <v>4530260427</v>
       </c>
-      <c r="P147" s="7" t="s">
+      <c r="R147" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>159</v>
       </c>
@@ -5522,11 +5535,11 @@
       <c r="M148" s="3">
         <v>4530263860</v>
       </c>
-      <c r="P148" s="7" t="s">
+      <c r="R148" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>160</v>
       </c>
@@ -5557,11 +5570,11 @@
       <c r="J149" s="3">
         <v>4466037745</v>
       </c>
-      <c r="P149" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R149" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>161</v>
       </c>
@@ -5589,11 +5602,11 @@
       <c r="I150" s="3">
         <v>4466038409</v>
       </c>
-      <c r="P150" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R150" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>162</v>
       </c>
@@ -5606,10 +5619,10 @@
       <c r="D151" s="3">
         <v>4445943218</v>
       </c>
-      <c r="E151" s="3">
+      <c r="E151" s="11">
         <v>3795461973</v>
       </c>
-      <c r="F151" s="3">
+      <c r="F151" s="17">
         <v>3863596639</v>
       </c>
       <c r="G151" s="3">
@@ -5630,11 +5643,11 @@
       <c r="L151" s="3">
         <v>4466036877</v>
       </c>
-      <c r="P151" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R151" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>163</v>
       </c>
@@ -5650,11 +5663,11 @@
       <c r="E152" s="3">
         <v>4466038208</v>
       </c>
-      <c r="P152" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R152" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>164</v>
       </c>
@@ -5685,11 +5698,11 @@
       <c r="J153" s="3">
         <v>4466035346</v>
       </c>
-      <c r="P153" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R153" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>165</v>
       </c>
@@ -5717,11 +5730,11 @@
       <c r="I154" s="3">
         <v>4466037689</v>
       </c>
-      <c r="P154" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R154" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>166</v>
       </c>
@@ -5752,11 +5765,11 @@
       <c r="J155" s="3">
         <v>4466038522</v>
       </c>
-      <c r="P155" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R155" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
         <v>167</v>
       </c>
@@ -5769,7 +5782,7 @@
       <c r="D156" s="3">
         <v>4445944074</v>
       </c>
-      <c r="E156" s="3">
+      <c r="E156" s="11">
         <v>3795460373</v>
       </c>
       <c r="F156" s="3">
@@ -5799,14 +5812,14 @@
       <c r="N156" s="3">
         <v>4413868976</v>
       </c>
-      <c r="O156" s="3">
+      <c r="O156" s="11">
         <v>4466043329</v>
       </c>
-      <c r="P156" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R156" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>168</v>
       </c>
@@ -5819,11 +5832,11 @@
       <c r="D157" s="3">
         <v>4466037450</v>
       </c>
-      <c r="P157" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R157" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
         <v>169</v>
       </c>
@@ -5854,11 +5867,11 @@
       <c r="J158" s="3">
         <v>4466038473</v>
       </c>
-      <c r="P158" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R158" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>170</v>
       </c>
@@ -5889,11 +5902,11 @@
       <c r="J159" s="3">
         <v>4466039691</v>
       </c>
-      <c r="P159" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R159" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>171</v>
       </c>
@@ -5909,11 +5922,11 @@
       <c r="E160" s="3">
         <v>4466044425</v>
       </c>
-      <c r="P160" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R160" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>172</v>
       </c>
@@ -5938,11 +5951,11 @@
       <c r="H161" s="3">
         <v>4155958460</v>
       </c>
-      <c r="P161" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="162" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R161" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>173</v>
       </c>
@@ -5973,11 +5986,11 @@
       <c r="J162" s="3">
         <v>4466038399</v>
       </c>
-      <c r="P162" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R162" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>174</v>
       </c>
@@ -6005,11 +6018,11 @@
       <c r="I163" s="3">
         <v>4466035620</v>
       </c>
-      <c r="P163" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R163" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
         <v>175</v>
       </c>
@@ -6022,11 +6035,11 @@
       <c r="D164" s="3">
         <v>4466037932</v>
       </c>
-      <c r="P164" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R164" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>176</v>
       </c>
@@ -6057,11 +6070,11 @@
       <c r="J165" s="3">
         <v>4466035884</v>
       </c>
-      <c r="P165" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R165" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
         <v>177</v>
       </c>
@@ -6077,11 +6090,11 @@
       <c r="E166" s="3">
         <v>4466037746</v>
       </c>
-      <c r="P166" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R166" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
         <v>178</v>
       </c>
@@ -6109,11 +6122,11 @@
       <c r="I167" s="3">
         <v>4466035006</v>
       </c>
-      <c r="P167" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R167" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
         <v>179</v>
       </c>
@@ -6141,11 +6154,11 @@
       <c r="I168" s="3">
         <v>4466038937</v>
       </c>
-      <c r="P168" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R168" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
         <v>180</v>
       </c>
@@ -6173,11 +6186,11 @@
       <c r="I169" s="3">
         <v>4466038455</v>
       </c>
-      <c r="P169" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R169" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
         <v>181</v>
       </c>
@@ -6214,11 +6227,11 @@
       <c r="L170" s="3">
         <v>4466037900</v>
       </c>
-      <c r="P170" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R170" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
         <v>182</v>
       </c>
@@ -6252,11 +6265,11 @@
       <c r="K171" s="3">
         <v>4466038598</v>
       </c>
-      <c r="P171" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R171" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
         <v>183</v>
       </c>
@@ -6284,11 +6297,11 @@
       <c r="I172" s="3">
         <v>4466035504</v>
       </c>
-      <c r="P172" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R172" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
         <v>184</v>
       </c>
@@ -6322,11 +6335,11 @@
       <c r="K173" s="3">
         <v>4466036190</v>
       </c>
-      <c r="P173" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R173" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
         <v>185</v>
       </c>
@@ -6363,11 +6376,11 @@
       <c r="L174" s="3">
         <v>4466035863</v>
       </c>
-      <c r="P174" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R174" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
         <v>186</v>
       </c>
@@ -6404,11 +6417,11 @@
       <c r="L175" s="3">
         <v>4466036686</v>
       </c>
-      <c r="P175" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R175" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="4" t="s">
         <v>187</v>
       </c>
@@ -6445,11 +6458,11 @@
       <c r="L176" s="3">
         <v>4466037441</v>
       </c>
-      <c r="P176" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R176" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
         <v>188</v>
       </c>
@@ -6486,874 +6499,2167 @@
       <c r="L177" s="3">
         <v>4466038631</v>
       </c>
-      <c r="P177" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R177" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
         <v>189</v>
       </c>
       <c r="B178" s="15">
         <v>1738651921</v>
       </c>
-      <c r="P178" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C178" s="3">
+        <v>4353317904</v>
+      </c>
+      <c r="D178" s="3">
+        <v>4691638158</v>
+      </c>
+      <c r="E178" s="3">
+        <v>3192429217</v>
+      </c>
+      <c r="F178" s="3">
+        <v>4530244165</v>
+      </c>
+      <c r="G178" s="3">
+        <v>4466036806</v>
+      </c>
+      <c r="R178" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
         <v>190</v>
       </c>
       <c r="B179" s="15">
         <v>1738651917</v>
       </c>
-      <c r="P179" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C179" s="3">
+        <v>4445935676</v>
+      </c>
+      <c r="D179" s="3">
+        <v>4445932751</v>
+      </c>
+      <c r="E179" s="3">
+        <v>3941702210</v>
+      </c>
+      <c r="F179" s="3">
+        <v>4752031304</v>
+      </c>
+      <c r="G179" s="3">
+        <v>4155958024</v>
+      </c>
+      <c r="H179" s="3">
+        <v>4158566770</v>
+      </c>
+      <c r="I179" s="3">
+        <v>3795461961</v>
+      </c>
+      <c r="J179" s="3">
+        <v>3189692769</v>
+      </c>
+      <c r="K179" s="3">
+        <v>3192428084</v>
+      </c>
+      <c r="L179" s="3">
+        <v>3192428084</v>
+      </c>
+      <c r="M179" s="3">
+        <v>4530229101</v>
+      </c>
+      <c r="N179" s="3">
+        <v>4466035062</v>
+      </c>
+      <c r="R179" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
         <v>191</v>
       </c>
       <c r="B180" s="15">
         <v>1738651829</v>
       </c>
-      <c r="P180" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="181" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C180" s="3">
+        <v>4445945079</v>
+      </c>
+      <c r="D180" s="3">
+        <v>4445945215</v>
+      </c>
+      <c r="E180" s="3">
+        <v>3941700528</v>
+      </c>
+      <c r="F180" s="3">
+        <v>4752034187</v>
+      </c>
+      <c r="G180" s="3">
+        <v>4155959339</v>
+      </c>
+      <c r="H180" s="3">
+        <v>4158566247</v>
+      </c>
+      <c r="I180" s="3">
+        <v>3795459992</v>
+      </c>
+      <c r="J180" s="3">
+        <v>3192429181</v>
+      </c>
+      <c r="K180" s="3">
+        <v>4530226387</v>
+      </c>
+      <c r="L180" s="3">
+        <v>4466037871</v>
+      </c>
+      <c r="R180" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="4" t="s">
         <v>192</v>
       </c>
       <c r="B181" s="15">
         <v>1738651613</v>
       </c>
-      <c r="P181" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C181" s="3">
+        <v>4445936267</v>
+      </c>
+      <c r="D181" s="3">
+        <v>4445944897</v>
+      </c>
+      <c r="E181" s="11">
+        <v>3795459701</v>
+      </c>
+      <c r="F181" s="3">
+        <v>3941777424</v>
+      </c>
+      <c r="G181" s="3">
+        <v>4752035507</v>
+      </c>
+      <c r="H181" s="3">
+        <v>4155958233</v>
+      </c>
+      <c r="I181" s="3">
+        <v>4158566763</v>
+      </c>
+      <c r="J181" s="3">
+        <v>4691552303</v>
+      </c>
+      <c r="K181" s="3">
+        <v>3189693633</v>
+      </c>
+      <c r="L181" s="3">
+        <v>3192428545</v>
+      </c>
+      <c r="M181" s="3">
+        <v>4504593464</v>
+      </c>
+      <c r="N181" s="3">
+        <v>4466035517</v>
+      </c>
+      <c r="R181" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="4" t="s">
         <v>193</v>
       </c>
       <c r="B182" s="15">
         <v>1738652966</v>
       </c>
-      <c r="P182" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="183" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R182" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
         <v>194</v>
       </c>
       <c r="B183" s="15">
         <v>1738651975</v>
       </c>
-      <c r="P183" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C183" s="3">
+        <v>4445936364</v>
+      </c>
+      <c r="D183" s="3">
+        <v>4445942632</v>
+      </c>
+      <c r="E183" s="3">
+        <v>4752028174</v>
+      </c>
+      <c r="F183" s="3">
+        <v>4158567869</v>
+      </c>
+      <c r="G183" s="3">
+        <v>4155957188</v>
+      </c>
+      <c r="H183" s="3">
+        <v>3795459034</v>
+      </c>
+      <c r="I183" s="3">
+        <v>3189693138</v>
+      </c>
+      <c r="J183" s="3">
+        <v>3192428860</v>
+      </c>
+      <c r="K183" s="3">
+        <v>4530225797</v>
+      </c>
+      <c r="L183" s="3">
+        <v>4466035459</v>
+      </c>
+      <c r="R183" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="4" t="s">
         <v>195</v>
       </c>
       <c r="B184" s="15">
         <v>1738652535</v>
       </c>
-      <c r="P184" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="185" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C184" s="3">
+        <v>4445946889</v>
+      </c>
+      <c r="D184" s="3">
+        <v>4445941357</v>
+      </c>
+      <c r="E184" s="3">
+        <v>3918766195</v>
+      </c>
+      <c r="F184" s="3">
+        <v>4666988701</v>
+      </c>
+      <c r="G184" s="3">
+        <v>3918761973</v>
+      </c>
+      <c r="H184" s="3">
+        <v>3795458230</v>
+      </c>
+      <c r="I184" s="3">
+        <v>4752031657</v>
+      </c>
+      <c r="J184" s="3">
+        <v>4158568421</v>
+      </c>
+      <c r="K184" s="3">
+        <v>4155958206</v>
+      </c>
+      <c r="L184" s="3">
+        <v>4678458693</v>
+      </c>
+      <c r="M184" s="3">
+        <v>4678461956</v>
+      </c>
+      <c r="N184" s="3">
+        <v>4678466774</v>
+      </c>
+      <c r="O184" s="3">
+        <v>3192428306</v>
+      </c>
+      <c r="P184" s="3">
+        <v>4530226304</v>
+      </c>
+      <c r="Q184" s="3">
+        <v>4466036148</v>
+      </c>
+      <c r="R184" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
         <v>196</v>
       </c>
       <c r="B185" s="15">
         <v>1738652490</v>
       </c>
-      <c r="P185" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C185" s="3">
+        <v>4445935630</v>
+      </c>
+      <c r="D185" s="3">
+        <v>4445930955</v>
+      </c>
+      <c r="E185" s="3">
+        <v>3795460613</v>
+      </c>
+      <c r="F185" s="3">
+        <v>4752031409</v>
+      </c>
+      <c r="G185" s="3">
+        <v>4155959676</v>
+      </c>
+      <c r="H185" s="3">
+        <v>4158565928</v>
+      </c>
+      <c r="I185" s="3">
+        <v>4691392412</v>
+      </c>
+      <c r="J185" s="3">
+        <v>3192427838</v>
+      </c>
+      <c r="K185" s="3">
+        <v>4530232810</v>
+      </c>
+      <c r="L185" s="3">
+        <v>4466039815</v>
+      </c>
+      <c r="R185" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
         <v>197</v>
       </c>
       <c r="B186" s="15">
         <v>1738651416</v>
       </c>
-      <c r="P186" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C186" s="3">
+        <v>4445940273</v>
+      </c>
+      <c r="D186" s="3">
+        <v>4445930290</v>
+      </c>
+      <c r="E186" s="3">
+        <v>3795463257</v>
+      </c>
+      <c r="F186" s="3">
+        <v>4155957931</v>
+      </c>
+      <c r="G186" s="3">
+        <v>4158565904</v>
+      </c>
+      <c r="H186" s="3">
+        <v>3192428077</v>
+      </c>
+      <c r="I186" s="3">
+        <v>4530238994</v>
+      </c>
+      <c r="J186" s="3">
+        <v>4466035561</v>
+      </c>
+      <c r="R186" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
         <v>198</v>
       </c>
       <c r="B187" s="15">
         <v>1738652147</v>
       </c>
-      <c r="P187" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C187" s="3">
+        <v>4445928132</v>
+      </c>
+      <c r="D187" s="3">
+        <v>4445932806</v>
+      </c>
+      <c r="E187" s="3">
+        <v>3795462634</v>
+      </c>
+      <c r="F187" s="3">
+        <v>4752034535</v>
+      </c>
+      <c r="G187" s="3">
+        <v>4158566649</v>
+      </c>
+      <c r="H187" s="3">
+        <v>4155957909</v>
+      </c>
+      <c r="I187" s="3">
+        <v>3189695349</v>
+      </c>
+      <c r="J187" s="3">
+        <v>3192428415</v>
+      </c>
+      <c r="K187" s="3">
+        <v>4466042957</v>
+      </c>
+      <c r="R187" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
         <v>199</v>
       </c>
       <c r="B188" s="15">
         <v>1738652745</v>
       </c>
-      <c r="P188" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C188" s="3">
+        <v>4445947330</v>
+      </c>
+      <c r="D188" s="3">
+        <v>4445925828</v>
+      </c>
+      <c r="E188" s="3">
+        <v>3795462410</v>
+      </c>
+      <c r="F188" s="3">
+        <v>4155958732</v>
+      </c>
+      <c r="G188" s="3">
+        <v>4752031941</v>
+      </c>
+      <c r="H188" s="3">
+        <v>4158568536</v>
+      </c>
+      <c r="I188" s="3">
+        <v>3192428248</v>
+      </c>
+      <c r="J188" s="3">
+        <v>4530086625</v>
+      </c>
+      <c r="K188" s="3">
+        <v>4515115572</v>
+      </c>
+      <c r="L188" s="3">
+        <v>4515115158</v>
+      </c>
+      <c r="M188" s="3">
+        <v>4466037729</v>
+      </c>
+      <c r="R188" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
         <v>200</v>
       </c>
       <c r="B189" s="15">
         <v>1738652902</v>
       </c>
-      <c r="P189" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C189" s="3">
+        <v>3941705111</v>
+      </c>
+      <c r="D189" s="3">
+        <v>4353367321</v>
+      </c>
+      <c r="E189" s="3">
+        <v>3189693491</v>
+      </c>
+      <c r="F189" s="3">
+        <v>3192428133</v>
+      </c>
+      <c r="G189" s="3">
+        <v>4466038333</v>
+      </c>
+      <c r="R189" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
         <v>201</v>
       </c>
       <c r="B190" s="15">
         <v>1738653148</v>
       </c>
-      <c r="P190" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C190" s="3">
+        <v>4445947552</v>
+      </c>
+      <c r="D190" s="3">
+        <v>4445958427</v>
+      </c>
+      <c r="E190" s="3">
+        <v>3918766067</v>
+      </c>
+      <c r="F190" s="3">
+        <v>3918763381</v>
+      </c>
+      <c r="G190" s="3">
+        <v>3795463240</v>
+      </c>
+      <c r="H190" s="3">
+        <v>4752034065</v>
+      </c>
+      <c r="I190" s="3">
+        <v>4155957390</v>
+      </c>
+      <c r="J190" s="3">
+        <v>4158565999</v>
+      </c>
+      <c r="K190" s="3">
+        <v>4678457936</v>
+      </c>
+      <c r="L190" s="3">
+        <v>4678461961</v>
+      </c>
+      <c r="M190" s="3">
+        <v>4678466408</v>
+      </c>
+      <c r="N190" s="3">
+        <v>3189696411</v>
+      </c>
+      <c r="O190" s="3">
+        <v>3192428230</v>
+      </c>
+      <c r="P190" s="3">
+        <v>4466039521</v>
+      </c>
+      <c r="Q190" s="3">
+        <v>4704577179</v>
+      </c>
+      <c r="R190" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
         <v>202</v>
       </c>
       <c r="B191" s="15">
         <v>1738652878</v>
       </c>
-      <c r="P191" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C191" s="3">
+        <v>4353321309</v>
+      </c>
+      <c r="D191" s="3">
+        <v>3192428969</v>
+      </c>
+      <c r="E191" s="3">
+        <v>4530232340</v>
+      </c>
+      <c r="F191" s="3">
+        <v>3189694519</v>
+      </c>
+      <c r="G191" s="3">
+        <v>4466048508</v>
+      </c>
+      <c r="R191" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="4" t="s">
         <v>203</v>
       </c>
       <c r="B192" s="15">
         <v>1738651684</v>
       </c>
-      <c r="P192" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C192" s="3">
+        <v>4445943244</v>
+      </c>
+      <c r="D192" s="3">
+        <v>4445974423</v>
+      </c>
+      <c r="E192" s="3">
+        <v>3795457653</v>
+      </c>
+      <c r="F192" s="3">
+        <v>4155959960</v>
+      </c>
+      <c r="G192" s="3">
+        <v>4752033199</v>
+      </c>
+      <c r="H192" s="3">
+        <v>4158565778</v>
+      </c>
+      <c r="I192" s="3">
+        <v>3189694473</v>
+      </c>
+      <c r="J192" s="3">
+        <v>4466037719</v>
+      </c>
+      <c r="R192" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
         <v>204</v>
       </c>
       <c r="B193" s="15">
         <v>1738651926</v>
       </c>
-      <c r="P193" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="194" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C193" s="3">
+        <v>4445945163</v>
+      </c>
+      <c r="D193" s="3">
+        <v>4445944446</v>
+      </c>
+      <c r="E193" s="3">
+        <v>4752029689</v>
+      </c>
+      <c r="F193" s="3">
+        <v>4158566735</v>
+      </c>
+      <c r="G193" s="3">
+        <v>4155957534</v>
+      </c>
+      <c r="H193" s="3">
+        <v>3795461924</v>
+      </c>
+      <c r="I193" s="3">
+        <v>2585324150</v>
+      </c>
+      <c r="J193" s="3">
+        <v>3189692807</v>
+      </c>
+      <c r="K193" s="3">
+        <v>3192427951</v>
+      </c>
+      <c r="L193" s="3">
+        <v>3116749113</v>
+      </c>
+      <c r="M193" s="3">
+        <v>4466040695</v>
+      </c>
+      <c r="R193" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="4" t="s">
         <v>205</v>
       </c>
       <c r="B194" s="15">
         <v>1738652063</v>
       </c>
-      <c r="P194" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="195" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C194" s="3">
+        <v>4445956771</v>
+      </c>
+      <c r="D194" s="3">
+        <v>4445934039</v>
+      </c>
+      <c r="E194" s="3">
+        <v>3795461654</v>
+      </c>
+      <c r="F194" s="3">
+        <v>4752032779</v>
+      </c>
+      <c r="G194" s="3">
+        <v>4155959285</v>
+      </c>
+      <c r="H194" s="3">
+        <v>4158565215</v>
+      </c>
+      <c r="I194" s="3">
+        <v>3189687572</v>
+      </c>
+      <c r="J194" s="3">
+        <v>3192428621</v>
+      </c>
+      <c r="K194" s="3">
+        <v>4466036579</v>
+      </c>
+      <c r="R194" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
         <v>206</v>
       </c>
       <c r="B195" s="15">
         <v>1738652367</v>
       </c>
-      <c r="P195" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="196" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C195" s="3">
+        <v>4445929618</v>
+      </c>
+      <c r="D195" s="3">
+        <v>4445938572</v>
+      </c>
+      <c r="E195" s="3">
+        <v>3795464771</v>
+      </c>
+      <c r="F195" s="3">
+        <v>4155959811</v>
+      </c>
+      <c r="G195" s="3">
+        <v>4752034581</v>
+      </c>
+      <c r="H195" s="3">
+        <v>4158565405</v>
+      </c>
+      <c r="I195" s="3">
+        <v>3189694698</v>
+      </c>
+      <c r="J195" s="3">
+        <v>3192428763</v>
+      </c>
+      <c r="K195" s="3">
+        <v>4530227420</v>
+      </c>
+      <c r="L195" s="3">
+        <v>4466040163</v>
+      </c>
+      <c r="R195" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
         <v>207</v>
       </c>
       <c r="B196" s="15">
         <v>1750741073</v>
       </c>
-      <c r="P196" s="12" t="s">
+      <c r="R196" s="12" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="197" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="4" t="s">
         <v>208</v>
       </c>
       <c r="B197" s="15">
         <v>1750745563</v>
       </c>
-      <c r="P197" s="12" t="s">
+      <c r="R197" s="12" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="198" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="4" t="s">
         <v>209</v>
       </c>
       <c r="B198" s="15">
         <v>1750746305</v>
       </c>
-      <c r="P198" s="12" t="s">
+      <c r="C198" s="3">
+        <v>2963303023</v>
+      </c>
+      <c r="D198" s="3">
+        <v>3171275498</v>
+      </c>
+      <c r="E198" s="3">
+        <v>3130414745</v>
+      </c>
+      <c r="F198" s="3">
+        <v>2873305803</v>
+      </c>
+      <c r="R198" s="12" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="199" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
         <v>210</v>
       </c>
       <c r="B199" s="15">
         <v>1750746301</v>
       </c>
-      <c r="P199" s="12" t="s">
+      <c r="R199" s="12" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="200" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="4" t="s">
         <v>211</v>
       </c>
       <c r="B200" s="15">
         <v>1750745566</v>
       </c>
-      <c r="P200" s="12" t="s">
+      <c r="C200" s="3">
+        <v>3918762265</v>
+      </c>
+      <c r="D200" s="3">
+        <v>3918765790</v>
+      </c>
+      <c r="E200" s="3">
+        <v>4016847417</v>
+      </c>
+      <c r="F200" s="3">
+        <v>3963925389</v>
+      </c>
+      <c r="G200" s="3">
+        <v>3833247232</v>
+      </c>
+      <c r="H200" s="3">
+        <v>4678457842</v>
+      </c>
+      <c r="I200" s="3">
+        <v>4678461002</v>
+      </c>
+      <c r="J200" s="3">
+        <v>4678466998</v>
+      </c>
+      <c r="R200" s="12" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="201" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
         <v>212</v>
       </c>
       <c r="B201" s="15">
         <v>1750745576</v>
       </c>
-      <c r="P201" s="12" t="s">
+      <c r="R201" s="12" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="202" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
         <v>213</v>
       </c>
       <c r="B202" s="15">
         <v>1849771468</v>
       </c>
-      <c r="P202" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C202" s="3">
+        <v>4445933084</v>
+      </c>
+      <c r="D202" s="3">
+        <v>4466040195</v>
+      </c>
+      <c r="E202" s="3">
+        <v>4158566719</v>
+      </c>
+      <c r="F202" s="3">
+        <v>4155957484</v>
+      </c>
+      <c r="G202" s="3">
+        <v>3795459379</v>
+      </c>
+      <c r="H202" s="3">
+        <v>4445934289</v>
+      </c>
+      <c r="R202" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
         <v>214</v>
       </c>
       <c r="B203" s="15">
         <v>1849777829</v>
       </c>
-      <c r="P203" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C203" s="3">
+        <v>4445948229</v>
+      </c>
+      <c r="D203" s="3">
+        <v>4445945770</v>
+      </c>
+      <c r="E203" s="3">
+        <v>3941773151</v>
+      </c>
+      <c r="F203" s="3">
+        <v>4155960160</v>
+      </c>
+      <c r="G203" s="3">
+        <v>4158565491</v>
+      </c>
+      <c r="H203" s="3">
+        <v>3795462158</v>
+      </c>
+      <c r="I203" s="3">
+        <v>4466035061</v>
+      </c>
+      <c r="R203" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="4" t="s">
         <v>215</v>
       </c>
       <c r="B204" s="15">
         <v>1849777981</v>
       </c>
-      <c r="P204" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="205" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C204" s="3">
+        <v>3941804865</v>
+      </c>
+      <c r="D204" s="3">
+        <v>4353331802</v>
+      </c>
+      <c r="E204" s="3">
+        <v>4466038559</v>
+      </c>
+      <c r="R204" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4" t="s">
         <v>216</v>
       </c>
       <c r="B205" s="15">
         <v>1849778110</v>
       </c>
-      <c r="P205" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C205" s="3">
+        <v>4445955621</v>
+      </c>
+      <c r="D205" s="3">
+        <v>4445939936</v>
+      </c>
+      <c r="E205" s="3">
+        <v>4158566744</v>
+      </c>
+      <c r="F205" s="3">
+        <v>4155957003</v>
+      </c>
+      <c r="G205" s="3">
+        <v>3795461881</v>
+      </c>
+      <c r="H205" s="3">
+        <v>4466036731</v>
+      </c>
+      <c r="R205" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4" t="s">
         <v>217</v>
       </c>
       <c r="B206" s="15">
         <v>1849777791</v>
       </c>
-      <c r="P206" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="207" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C206" s="3">
+        <v>3941773834</v>
+      </c>
+      <c r="D206" s="3">
+        <v>4155959084</v>
+      </c>
+      <c r="E206" s="17">
+        <v>3795462481</v>
+      </c>
+      <c r="R206" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
         <v>218</v>
       </c>
       <c r="B207" s="15">
         <v>1849777893</v>
       </c>
-      <c r="P207" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C207" s="3">
+        <v>4445940526</v>
+      </c>
+      <c r="D207" s="3">
+        <v>4445946719</v>
+      </c>
+      <c r="E207" s="3">
+        <v>4158567233</v>
+      </c>
+      <c r="F207" s="3">
+        <v>4155959193</v>
+      </c>
+      <c r="G207" s="3">
+        <v>3795463990</v>
+      </c>
+      <c r="H207" s="3">
+        <v>4466040339</v>
+      </c>
+      <c r="R207" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4" t="s">
         <v>219</v>
       </c>
       <c r="B208" s="15">
         <v>1849777815</v>
       </c>
-      <c r="P208" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="209" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R208" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
         <v>220</v>
       </c>
       <c r="B209" s="15">
         <v>1849777581</v>
       </c>
-      <c r="P209" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C209" s="3">
+        <v>4445936838</v>
+      </c>
+      <c r="D209" s="3">
+        <v>4445933928</v>
+      </c>
+      <c r="E209" s="3">
+        <v>4158567892</v>
+      </c>
+      <c r="F209" s="3">
+        <v>3795464305</v>
+      </c>
+      <c r="G209" s="3">
+        <v>4155960227</v>
+      </c>
+      <c r="H209" s="3">
+        <v>4466036961</v>
+      </c>
+      <c r="R209" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
         <v>221</v>
       </c>
       <c r="B210" s="15">
         <v>1849777716</v>
       </c>
-      <c r="P210" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D210" s="3">
+        <v>4445964232</v>
+      </c>
+      <c r="E210" s="3">
+        <v>4445964232</v>
+      </c>
+      <c r="F210" s="3">
+        <v>4158566748</v>
+      </c>
+      <c r="G210" s="3">
+        <v>3795460864</v>
+      </c>
+      <c r="H210" s="3">
+        <v>3795460864</v>
+      </c>
+      <c r="I210" s="17">
+        <v>4155958078</v>
+      </c>
+      <c r="R210" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
         <v>222</v>
       </c>
       <c r="B211" s="15">
         <v>1849777650</v>
       </c>
-      <c r="P211" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C211" s="3">
+        <v>4445954437</v>
+      </c>
+      <c r="D211" s="3">
+        <v>4445960805</v>
+      </c>
+      <c r="E211" s="3">
+        <v>3795459613</v>
+      </c>
+      <c r="F211" s="3">
+        <v>3941712959</v>
+      </c>
+      <c r="G211" s="3">
+        <v>4158565731</v>
+      </c>
+      <c r="H211" s="3">
+        <v>4155959337</v>
+      </c>
+      <c r="I211" s="3">
+        <v>4466038216</v>
+      </c>
+      <c r="R211" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="4" t="s">
         <v>223</v>
       </c>
       <c r="B212" s="15">
         <v>1849778040</v>
       </c>
-      <c r="P212" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="213" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C212" s="3">
+        <v>4445946217</v>
+      </c>
+      <c r="D212" s="3">
+        <v>4445947934</v>
+      </c>
+      <c r="E212" s="3">
+        <v>3941713895</v>
+      </c>
+      <c r="F212" s="3">
+        <v>3795460692</v>
+      </c>
+      <c r="G212" s="3">
+        <v>4155956931</v>
+      </c>
+      <c r="H212" s="3">
+        <v>4158565564</v>
+      </c>
+      <c r="I212" s="3">
+        <v>4466038349</v>
+      </c>
+      <c r="R212" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
         <v>224</v>
       </c>
       <c r="B213" s="15">
         <v>1849777940</v>
       </c>
-      <c r="P213" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C213" s="3">
+        <v>4445949007</v>
+      </c>
+      <c r="D213" s="3">
+        <v>4445938898</v>
+      </c>
+      <c r="E213" s="3">
+        <v>3941720040</v>
+      </c>
+      <c r="F213" s="3">
+        <v>3795458750</v>
+      </c>
+      <c r="G213" s="3">
+        <v>4158566897</v>
+      </c>
+      <c r="H213" s="3">
+        <v>4155958175</v>
+      </c>
+      <c r="I213" s="3">
+        <v>4466036644</v>
+      </c>
+      <c r="R213" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
         <v>225</v>
       </c>
       <c r="B214" s="15">
         <v>1849778044</v>
       </c>
-      <c r="P214" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C214" s="3">
+        <v>4445990578</v>
+      </c>
+      <c r="D214" s="3">
+        <v>4445959569</v>
+      </c>
+      <c r="E214" s="3">
+        <v>3941712389</v>
+      </c>
+      <c r="F214" s="3">
+        <v>4158565313</v>
+      </c>
+      <c r="G214" s="3">
+        <v>4155959503</v>
+      </c>
+      <c r="H214" s="3">
+        <v>3795459991</v>
+      </c>
+      <c r="I214" s="3">
+        <v>4466038051</v>
+      </c>
+      <c r="R214" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
         <v>226</v>
       </c>
       <c r="B215" s="15">
         <v>1849777586</v>
       </c>
-      <c r="P215" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C215" s="3">
+        <v>4445944999</v>
+      </c>
+      <c r="D215" s="3">
+        <v>4445944288</v>
+      </c>
+      <c r="E215" s="3">
+        <v>3795462375</v>
+      </c>
+      <c r="F215" s="3">
+        <v>4155958141</v>
+      </c>
+      <c r="G215" s="3">
+        <v>4158566589</v>
+      </c>
+      <c r="H215" s="3">
+        <v>4466037604</v>
+      </c>
+      <c r="R215" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
         <v>227</v>
       </c>
       <c r="B216" s="15">
         <v>1849778023</v>
       </c>
-      <c r="P216" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="217" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C216" s="3">
+        <v>4445942835</v>
+      </c>
+      <c r="D216" s="3">
+        <v>4445937207</v>
+      </c>
+      <c r="E216" s="3">
+        <v>3795461635</v>
+      </c>
+      <c r="F216" s="3">
+        <v>3941701930</v>
+      </c>
+      <c r="G216" s="3">
+        <v>4155958676</v>
+      </c>
+      <c r="H216" s="3">
+        <v>4158569445</v>
+      </c>
+      <c r="I216" s="3">
+        <v>4466037064</v>
+      </c>
+      <c r="R216" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4" t="s">
         <v>228</v>
       </c>
       <c r="B217" s="15">
         <v>1849777600</v>
       </c>
-      <c r="P217" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="218" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C217" s="3">
+        <v>4445938566</v>
+      </c>
+      <c r="D217" s="3">
+        <v>4445937206</v>
+      </c>
+      <c r="E217" s="3">
+        <v>4158566491</v>
+      </c>
+      <c r="F217" s="3">
+        <v>4155957823</v>
+      </c>
+      <c r="G217" s="3">
+        <v>3795462373</v>
+      </c>
+      <c r="H217" s="3">
+        <v>4466043035</v>
+      </c>
+      <c r="R217" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
         <v>229</v>
       </c>
       <c r="B218" s="15">
         <v>1849777647</v>
       </c>
-      <c r="P218" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="219" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C218" s="3">
+        <v>4445958117</v>
+      </c>
+      <c r="D218" s="3">
+        <v>4445940731</v>
+      </c>
+      <c r="E218" s="3">
+        <v>3941706462</v>
+      </c>
+      <c r="F218" s="3">
+        <v>3941706462</v>
+      </c>
+      <c r="G218" s="3">
+        <v>3941706462</v>
+      </c>
+      <c r="H218" s="3">
+        <v>3795460330</v>
+      </c>
+      <c r="I218" s="3">
+        <v>4466037076</v>
+      </c>
+      <c r="J218" s="17">
+        <v>4158567047</v>
+      </c>
+      <c r="R218" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4" t="s">
         <v>230</v>
       </c>
       <c r="B219" s="15">
         <v>1849777720</v>
       </c>
-      <c r="P219" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="220" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C219" s="3">
+        <v>4445947889</v>
+      </c>
+      <c r="D219" s="3">
+        <v>4445944814</v>
+      </c>
+      <c r="E219" s="3">
+        <v>3941707517</v>
+      </c>
+      <c r="F219" s="3">
+        <v>4158568379</v>
+      </c>
+      <c r="G219" s="3">
+        <v>4155956914</v>
+      </c>
+      <c r="H219" s="3">
+        <v>3795461606</v>
+      </c>
+      <c r="I219" s="3">
+        <v>4466038760</v>
+      </c>
+      <c r="R219" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
         <v>231</v>
       </c>
       <c r="B220" s="15">
         <v>1849777551</v>
       </c>
-      <c r="P220" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="221" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C220" s="3">
+        <v>4353368274</v>
+      </c>
+      <c r="D220" s="3">
+        <v>4466038538</v>
+      </c>
+      <c r="R220" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
         <v>232</v>
       </c>
       <c r="B221" s="15">
         <v>1849778151</v>
       </c>
-      <c r="P221" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="222" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C221" s="3">
+        <v>4445930816</v>
+      </c>
+      <c r="D221" s="3">
+        <v>4445932927</v>
+      </c>
+      <c r="E221" s="3">
+        <v>3795460455</v>
+      </c>
+      <c r="F221" s="3">
+        <v>4158566179</v>
+      </c>
+      <c r="G221" s="3">
+        <v>4155957759</v>
+      </c>
+      <c r="H221" s="3">
+        <v>4466036486</v>
+      </c>
+      <c r="R221" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
         <v>233</v>
       </c>
       <c r="B222" s="15">
         <v>1849777651</v>
       </c>
-      <c r="P222" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="223" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C222" s="3">
+        <v>4445942889</v>
+      </c>
+      <c r="D222" s="3">
+        <v>4445934240</v>
+      </c>
+      <c r="E222" s="3">
+        <v>3795462786</v>
+      </c>
+      <c r="F222" s="3">
+        <v>4155960434</v>
+      </c>
+      <c r="G222" s="3">
+        <v>4158566564</v>
+      </c>
+      <c r="H222" s="3">
+        <v>4466047741</v>
+      </c>
+      <c r="R222" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
         <v>234</v>
       </c>
       <c r="B223" s="15">
         <v>1849777656</v>
       </c>
-      <c r="P223" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="224" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C223" s="3">
+        <v>4445959873</v>
+      </c>
+      <c r="D223" s="3">
+        <v>4445960357</v>
+      </c>
+      <c r="E223" s="3">
+        <v>3795459270</v>
+      </c>
+      <c r="F223" s="3">
+        <v>4155956901</v>
+      </c>
+      <c r="G223" s="3">
+        <v>4158565494</v>
+      </c>
+      <c r="H223" s="3">
+        <v>4466036439</v>
+      </c>
+      <c r="R223" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
         <v>235</v>
       </c>
       <c r="B224" s="15">
         <v>1849777833</v>
       </c>
-      <c r="P224" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="225" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C224" s="3">
+        <v>4445941659</v>
+      </c>
+      <c r="D224" s="3">
+        <v>4445934938</v>
+      </c>
+      <c r="E224" s="3">
+        <v>3941709512</v>
+      </c>
+      <c r="F224" s="3">
+        <v>4155959166</v>
+      </c>
+      <c r="G224" s="3">
+        <v>4158567063</v>
+      </c>
+      <c r="H224" s="3">
+        <v>3795459914</v>
+      </c>
+      <c r="I224" s="3">
+        <v>4411159826</v>
+      </c>
+      <c r="J224" s="3">
+        <v>4466038939</v>
+      </c>
+      <c r="R224" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="225" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
         <v>236</v>
       </c>
       <c r="B225" s="15">
         <v>1849777906</v>
       </c>
-      <c r="P225" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C225" s="3">
+        <v>4445943614</v>
+      </c>
+      <c r="D225" s="3">
+        <v>4445935774</v>
+      </c>
+      <c r="E225" s="3">
+        <v>4155959415</v>
+      </c>
+      <c r="F225" s="3">
+        <v>4158566851</v>
+      </c>
+      <c r="G225" s="3">
+        <v>3795461573</v>
+      </c>
+      <c r="H225" s="3">
+        <v>4466036655</v>
+      </c>
+      <c r="R225" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="226" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
         <v>237</v>
       </c>
       <c r="B226" s="15">
         <v>1849777862</v>
       </c>
-      <c r="P226" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C226" s="3">
+        <v>4445952553</v>
+      </c>
+      <c r="D226" s="3">
+        <v>4445941244</v>
+      </c>
+      <c r="E226" s="3">
+        <v>4158567025</v>
+      </c>
+      <c r="F226" s="3">
+        <v>4155957892</v>
+      </c>
+      <c r="G226" s="3">
+        <v>3795461338</v>
+      </c>
+      <c r="H226" s="3">
+        <v>4466037503</v>
+      </c>
+      <c r="R226" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="227" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
         <v>238</v>
       </c>
       <c r="B227" s="15">
         <v>1912188679</v>
       </c>
-      <c r="P227" s="9" t="s">
+      <c r="C227" s="3">
+        <v>3795517502</v>
+      </c>
+      <c r="D227" s="3">
+        <v>2914033211</v>
+      </c>
+      <c r="E227" s="3">
+        <v>2958903561</v>
+      </c>
+      <c r="F227" s="3">
+        <v>2816666292</v>
+      </c>
+      <c r="G227" s="3">
+        <v>4544783294</v>
+      </c>
+      <c r="R227" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="228" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
         <v>239</v>
       </c>
       <c r="B228" s="15">
         <v>1912201998</v>
       </c>
-      <c r="P228" s="9" t="s">
+      <c r="C228" s="3">
+        <v>3795518352</v>
+      </c>
+      <c r="D228" s="3">
+        <v>2914045558</v>
+      </c>
+      <c r="E228" s="3">
+        <v>2958902409</v>
+      </c>
+      <c r="F228" s="3">
+        <v>2958902409</v>
+      </c>
+      <c r="G228" s="3">
+        <v>2958902409</v>
+      </c>
+      <c r="R228" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="229" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
         <v>240</v>
       </c>
       <c r="B229" s="15">
         <v>1912202740</v>
       </c>
-      <c r="P229" s="9" t="s">
+      <c r="C229" s="3">
+        <v>3795520609</v>
+      </c>
+      <c r="D229" s="3">
+        <v>2958901054</v>
+      </c>
+      <c r="E229" s="3">
+        <v>2816667718</v>
+      </c>
+      <c r="F229" s="3">
+        <v>2816667718</v>
+      </c>
+      <c r="G229" s="3">
+        <v>2914016450</v>
+      </c>
+      <c r="H229" s="3">
+        <v>4544787002</v>
+      </c>
+      <c r="R229" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="230" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
         <v>241</v>
       </c>
       <c r="B230" s="15">
         <v>1912202107</v>
       </c>
-      <c r="P230" s="9" t="s">
+      <c r="C230" s="3">
+        <v>2914019289</v>
+      </c>
+      <c r="D230" s="3">
+        <v>2958902366</v>
+      </c>
+      <c r="E230" s="3">
+        <v>2816666843</v>
+      </c>
+      <c r="F230" s="3">
+        <v>4544787784</v>
+      </c>
+      <c r="R230" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="231" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4" t="s">
         <v>242</v>
       </c>
       <c r="B231" s="15">
         <v>1912202149</v>
       </c>
-      <c r="P231" s="9" t="s">
+      <c r="C231" s="3">
+        <v>3795517904</v>
+      </c>
+      <c r="D231" s="3">
+        <v>2914016241</v>
+      </c>
+      <c r="E231" s="3">
+        <v>2958902802</v>
+      </c>
+      <c r="F231" s="3">
+        <v>2816667013</v>
+      </c>
+      <c r="G231" s="3">
+        <v>2816667013</v>
+      </c>
+      <c r="R231" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="232" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4" t="s">
         <v>243</v>
       </c>
       <c r="B232" s="15">
         <v>1912201742</v>
       </c>
-      <c r="P232" s="9" t="s">
+      <c r="C232" s="3">
+        <v>3795518034</v>
+      </c>
+      <c r="D232" s="3">
+        <v>2914029819</v>
+      </c>
+      <c r="E232" s="3">
+        <v>2958903452</v>
+      </c>
+      <c r="F232" s="3">
+        <v>2816667825</v>
+      </c>
+      <c r="G232" s="3">
+        <v>4544785767</v>
+      </c>
+      <c r="R232" s="9" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="233" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4" t="s">
         <v>244</v>
       </c>
       <c r="B233" s="15">
         <v>1912202033</v>
       </c>
-      <c r="P233" s="7" t="s">
+      <c r="C233" s="3">
+        <v>4026431102</v>
+      </c>
+      <c r="D233" s="3">
+        <v>4026432800</v>
+      </c>
+      <c r="E233" s="3">
+        <v>3795516245</v>
+      </c>
+      <c r="F233" s="3">
+        <v>4506827493</v>
+      </c>
+      <c r="G233" s="3">
+        <v>4544790105</v>
+      </c>
+      <c r="R233" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="234" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
         <v>245</v>
       </c>
       <c r="B234" s="15">
         <v>1912202814</v>
       </c>
-      <c r="P234" s="7" t="s">
+      <c r="C234" s="3">
+        <v>3795518379</v>
+      </c>
+      <c r="D234" s="3">
+        <v>3795518379</v>
+      </c>
+      <c r="E234" s="3">
+        <v>2958902493</v>
+      </c>
+      <c r="F234" s="3">
+        <v>2816667832</v>
+      </c>
+      <c r="G234" s="3">
+        <v>4431537736</v>
+      </c>
+      <c r="H234" s="3">
+        <v>4544790331</v>
+      </c>
+      <c r="R234" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="235" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="4" t="s">
         <v>246</v>
       </c>
       <c r="B235" s="15">
         <v>1912202105</v>
       </c>
-      <c r="P235" s="7" t="s">
+      <c r="C235" s="3">
+        <v>3795521511</v>
+      </c>
+      <c r="D235" s="3">
+        <v>2914036882</v>
+      </c>
+      <c r="E235" s="3">
+        <v>2958902660</v>
+      </c>
+      <c r="F235" s="3">
+        <v>2816666760</v>
+      </c>
+      <c r="G235" s="3">
+        <v>4544786743</v>
+      </c>
+      <c r="R235" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="236" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
         <v>247</v>
       </c>
       <c r="B236" s="15">
         <v>1912202818</v>
       </c>
-      <c r="P236" s="7" t="s">
+      <c r="C236" s="3">
+        <v>3795519487</v>
+      </c>
+      <c r="D236" s="3">
+        <v>4544784970</v>
+      </c>
+      <c r="R236" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="237" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
         <v>248</v>
       </c>
       <c r="B237" s="15">
         <v>1912202795</v>
       </c>
-      <c r="P237" s="7" t="s">
+      <c r="C237" s="3">
+        <v>3795517197</v>
+      </c>
+      <c r="D237" s="3">
+        <v>4544787298</v>
+      </c>
+      <c r="R237" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="238" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="4" t="s">
         <v>249</v>
       </c>
       <c r="B238" s="15">
         <v>1912202099</v>
       </c>
-      <c r="P238" s="7" t="s">
+      <c r="C238" s="3">
+        <v>3795522006</v>
+      </c>
+      <c r="D238" s="3">
+        <v>2816667668</v>
+      </c>
+      <c r="E238" s="3">
+        <v>3032684706</v>
+      </c>
+      <c r="F238" s="3">
+        <v>2914019940</v>
+      </c>
+      <c r="G238" s="3">
+        <v>4544786926</v>
+      </c>
+      <c r="R238" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="239" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
         <v>250</v>
       </c>
       <c r="B239" s="15">
         <v>1912202725</v>
       </c>
-      <c r="P239" s="7" t="s">
+      <c r="C239" s="3">
+        <v>3795518306</v>
+      </c>
+      <c r="D239" s="3">
+        <v>2914032400</v>
+      </c>
+      <c r="E239" s="3">
+        <v>2958903639</v>
+      </c>
+      <c r="F239" s="3">
+        <v>2816666627</v>
+      </c>
+      <c r="G239" s="3">
+        <v>4544793601</v>
+      </c>
+      <c r="R239" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="240" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4" t="s">
         <v>251</v>
       </c>
       <c r="B240" s="15">
         <v>1912202762</v>
       </c>
-      <c r="P240" s="7" t="s">
+      <c r="C240" s="3">
+        <v>4027363009</v>
+      </c>
+      <c r="D240" s="3">
+        <v>3795520829</v>
+      </c>
+      <c r="E240" s="3">
+        <v>2914017293</v>
+      </c>
+      <c r="F240" s="3">
+        <v>2958902846</v>
+      </c>
+      <c r="G240" s="3">
+        <v>2816666984</v>
+      </c>
+      <c r="H240" s="3">
+        <v>4544791449</v>
+      </c>
+      <c r="R240" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="241" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
         <v>252</v>
       </c>
       <c r="B241" s="15">
         <v>1912202800</v>
       </c>
-      <c r="P241" s="7" t="s">
+      <c r="C241" s="3">
+        <v>2914025488</v>
+      </c>
+      <c r="D241" s="3">
+        <v>2958902830</v>
+      </c>
+      <c r="E241" s="3">
+        <v>2816667080</v>
+      </c>
+      <c r="F241" s="3">
+        <v>4544789986</v>
+      </c>
+      <c r="R241" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="242" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
         <v>253</v>
       </c>
       <c r="B242" s="15">
         <v>1912202625</v>
       </c>
-      <c r="P242" s="7" t="s">
+      <c r="C242" s="3">
+        <v>2914014483</v>
+      </c>
+      <c r="D242" s="3">
+        <v>2816667773</v>
+      </c>
+      <c r="E242" s="3">
+        <v>4544784513</v>
+      </c>
+      <c r="R242" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="243" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="4" t="s">
         <v>254</v>
       </c>
       <c r="B243" s="15">
         <v>1912202150</v>
       </c>
-      <c r="P243" s="7" t="s">
+      <c r="C243" s="3">
+        <v>3795518757</v>
+      </c>
+      <c r="D243" s="3">
+        <v>2958901435</v>
+      </c>
+      <c r="E243" s="3">
+        <v>2816667192</v>
+      </c>
+      <c r="F243" s="3">
+        <v>3032680221</v>
+      </c>
+      <c r="G243" s="3">
+        <v>2914015073</v>
+      </c>
+      <c r="H243" s="3">
+        <v>4544787591</v>
+      </c>
+      <c r="R243" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="244" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="4" t="s">
         <v>255</v>
       </c>
       <c r="B244" s="15">
         <v>1912202508</v>
       </c>
-      <c r="P244" s="7" t="s">
+      <c r="C244" s="3">
+        <v>3795517301</v>
+      </c>
+      <c r="D244" s="3">
+        <v>4544785342</v>
+      </c>
+      <c r="R244" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="245" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
         <v>256</v>
       </c>
       <c r="B245" s="15">
         <v>1912202516</v>
       </c>
-      <c r="P245" s="7" t="s">
+      <c r="C245" s="3">
+        <v>3795519028</v>
+      </c>
+      <c r="D245" s="3">
+        <v>4544788944</v>
+      </c>
+      <c r="R245" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="246" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
         <v>257</v>
       </c>
       <c r="B246" s="15">
         <v>1912202637</v>
       </c>
-      <c r="P246" s="7" t="s">
+      <c r="C246" s="3">
+        <v>3795521723</v>
+      </c>
+      <c r="D246" s="3">
+        <v>2958903342</v>
+      </c>
+      <c r="E246" s="3">
+        <v>2816667678</v>
+      </c>
+      <c r="F246" s="3">
+        <v>2914035339</v>
+      </c>
+      <c r="G246" s="3">
+        <v>4544795083</v>
+      </c>
+      <c r="R246" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="247" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
         <v>258</v>
       </c>
       <c r="B247" s="15">
         <v>1912201812</v>
       </c>
-      <c r="P247" s="7" t="s">
+      <c r="C247" s="3">
+        <v>3795520520</v>
+      </c>
+      <c r="D247" s="3">
+        <v>2958901002</v>
+      </c>
+      <c r="E247" s="3">
+        <v>2914014172</v>
+      </c>
+      <c r="F247" s="3">
+        <v>4544792565</v>
+      </c>
+      <c r="G247" s="3">
+        <v>2816667055</v>
+      </c>
+      <c r="R247" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="248" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
         <v>259</v>
       </c>
       <c r="B248" s="15">
         <v>1912202756</v>
       </c>
-      <c r="P248" s="7" t="s">
+      <c r="C248" s="3">
+        <v>3795517490</v>
+      </c>
+      <c r="D248" s="3">
+        <v>4544786827</v>
+      </c>
+      <c r="R248" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="249" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
         <v>260</v>
       </c>
       <c r="B249" s="15">
         <v>1912202590</v>
       </c>
-      <c r="P249" s="7" t="s">
+      <c r="C249" s="3">
+        <v>3795518858</v>
+      </c>
+      <c r="D249" s="3">
+        <v>4544789585</v>
+      </c>
+      <c r="R249" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="250" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
         <v>261</v>
       </c>
       <c r="B250" s="15">
         <v>1912202058</v>
       </c>
-      <c r="P250" s="7" t="s">
+      <c r="C250" s="3">
+        <v>3795517361</v>
+      </c>
+      <c r="D250" s="3">
+        <v>2914016057</v>
+      </c>
+      <c r="E250" s="3">
+        <v>2958902040</v>
+      </c>
+      <c r="F250" s="3">
+        <v>2816666479</v>
+      </c>
+      <c r="G250" s="3">
+        <v>4544787536</v>
+      </c>
+      <c r="R250" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="251" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
         <v>262</v>
       </c>
       <c r="B251" s="15">
         <v>2449977854</v>
       </c>
-      <c r="P251" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X251" s="11"/>
-    </row>
-    <row r="252" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C251" s="3">
+        <v>3795498072</v>
+      </c>
+      <c r="R251" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z251" s="11"/>
+    </row>
+    <row r="252" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
         <v>263</v>
       </c>
       <c r="B252" s="15">
         <v>2449977213</v>
       </c>
-      <c r="P252" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X252" s="11"/>
-    </row>
-    <row r="253" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C252" s="3">
+        <v>3795500281</v>
+      </c>
+      <c r="R252" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z252" s="11"/>
+    </row>
+    <row r="253" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
         <v>264</v>
       </c>
       <c r="B253" s="15">
         <v>2449975997</v>
       </c>
-      <c r="P253" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X253" s="11"/>
-    </row>
-    <row r="254" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C253" s="3">
+        <v>3795496267</v>
+      </c>
+      <c r="D253" s="3">
+        <v>4411168623</v>
+      </c>
+      <c r="R253" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z253" s="11"/>
+    </row>
+    <row r="254" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
         <v>265</v>
       </c>
       <c r="B254" s="15">
         <v>2449977489</v>
       </c>
-      <c r="P254" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X254" s="11"/>
-    </row>
-    <row r="255" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C254" s="3">
+        <v>3795496463</v>
+      </c>
+      <c r="D254" s="3">
+        <v>4411168300</v>
+      </c>
+      <c r="R254" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z254" s="11"/>
+    </row>
+    <row r="255" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
         <v>266</v>
       </c>
       <c r="B255" s="15">
         <v>2449979646</v>
       </c>
-      <c r="P255" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X255" s="11"/>
-    </row>
-    <row r="256" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C255" s="3">
+        <v>3795497550</v>
+      </c>
+      <c r="R255" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z255" s="11"/>
+    </row>
+    <row r="256" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
         <v>267</v>
       </c>
@@ -7363,12 +8669,12 @@
       <c r="C256" s="5">
         <v>3795497894</v>
       </c>
-      <c r="P256" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X256" s="11"/>
-    </row>
-    <row r="257" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R256" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z256" s="11"/>
+    </row>
+    <row r="257" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
         <v>268</v>
       </c>
@@ -7381,24 +8687,24 @@
       <c r="D257" s="3">
         <v>4411172564</v>
       </c>
-      <c r="P257" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X257" s="11"/>
-    </row>
-    <row r="258" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R257" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z257" s="11"/>
+    </row>
+    <row r="258" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
         <v>269</v>
       </c>
       <c r="B258" s="15">
         <v>2449978285</v>
       </c>
-      <c r="P258" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X258" s="11"/>
-    </row>
-    <row r="259" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R258" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z258" s="11"/>
+    </row>
+    <row r="259" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
         <v>270</v>
       </c>
@@ -7420,12 +8726,12 @@
       <c r="G259" s="3">
         <v>4411169009</v>
       </c>
-      <c r="P259" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X259" s="11"/>
-    </row>
-    <row r="260" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R259" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z259" s="11"/>
+    </row>
+    <row r="260" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
         <v>271</v>
       </c>
@@ -7435,12 +8741,12 @@
       <c r="C260" s="3">
         <v>3795498107</v>
       </c>
-      <c r="P260" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X260" s="11"/>
-    </row>
-    <row r="261" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R260" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z260" s="11"/>
+    </row>
+    <row r="261" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
         <v>272</v>
       </c>
@@ -7450,12 +8756,12 @@
       <c r="C261" s="5">
         <v>4411169482</v>
       </c>
-      <c r="P261" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X261" s="11"/>
-    </row>
-    <row r="262" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R261" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z261" s="11"/>
+    </row>
+    <row r="262" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
         <v>273</v>
       </c>
@@ -7468,12 +8774,12 @@
       <c r="D262" s="3">
         <v>4411163271</v>
       </c>
-      <c r="P262" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X262" s="11"/>
-    </row>
-    <row r="263" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R262" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z262" s="11"/>
+    </row>
+    <row r="263" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
         <v>274</v>
       </c>
@@ -7486,12 +8792,12 @@
       <c r="D263" s="3">
         <v>4411169394</v>
       </c>
-      <c r="P263" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X263" s="11"/>
-    </row>
-    <row r="264" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R263" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z263" s="11"/>
+    </row>
+    <row r="264" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>275</v>
       </c>
@@ -7501,12 +8807,12 @@
       <c r="C264" s="3">
         <v>4411164044</v>
       </c>
-      <c r="P264" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X264" s="11"/>
-    </row>
-    <row r="265" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R264" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z264" s="11"/>
+    </row>
+    <row r="265" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
         <v>276</v>
       </c>
@@ -7516,12 +8822,12 @@
       <c r="C265" s="3">
         <v>3795498609</v>
       </c>
-      <c r="P265" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X265" s="11"/>
-    </row>
-    <row r="266" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R265" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z265" s="11"/>
+    </row>
+    <row r="266" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
         <v>277</v>
       </c>
@@ -7531,12 +8837,12 @@
       <c r="C266" s="3">
         <v>4411169474</v>
       </c>
-      <c r="P266" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X266" s="11"/>
-    </row>
-    <row r="267" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R266" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z266" s="11"/>
+    </row>
+    <row r="267" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
         <v>278</v>
       </c>
@@ -7549,12 +8855,12 @@
       <c r="D267" s="3">
         <v>4411162694</v>
       </c>
-      <c r="P267" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X267" s="11"/>
-    </row>
-    <row r="268" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R267" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z267" s="11"/>
+    </row>
+    <row r="268" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
         <v>279</v>
       </c>
@@ -7570,12 +8876,12 @@
       <c r="E268" s="3">
         <v>4724087547</v>
       </c>
-      <c r="P268" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X268" s="11"/>
-    </row>
-    <row r="269" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R268" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z268" s="11"/>
+    </row>
+    <row r="269" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4" t="s">
         <v>280</v>
       </c>
@@ -7588,12 +8894,12 @@
       <c r="D269" s="3">
         <v>4411169297</v>
       </c>
-      <c r="P269" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X269" s="11"/>
-    </row>
-    <row r="270" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R269" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z269" s="11"/>
+    </row>
+    <row r="270" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
         <v>281</v>
       </c>
@@ -7606,12 +8912,12 @@
       <c r="D270" s="3">
         <v>4724083911</v>
       </c>
-      <c r="P270" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X270" s="11"/>
-    </row>
-    <row r="271" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R270" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z270" s="11"/>
+    </row>
+    <row r="271" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="4" t="s">
         <v>282</v>
       </c>
@@ -7621,12 +8927,12 @@
       <c r="C271" s="3">
         <v>3795497092</v>
       </c>
-      <c r="P271" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X271" s="11"/>
-    </row>
-    <row r="272" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R271" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z271" s="11"/>
+    </row>
+    <row r="272" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="4" t="s">
         <v>283</v>
       </c>
@@ -7636,12 +8942,12 @@
       <c r="C272" s="3">
         <v>3795498347</v>
       </c>
-      <c r="P272" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X272" s="11"/>
-    </row>
-    <row r="273" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R272" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z272" s="11"/>
+    </row>
+    <row r="273" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
         <v>284</v>
       </c>
@@ -7651,12 +8957,12 @@
       <c r="C273" s="3">
         <v>3795497485</v>
       </c>
-      <c r="P273" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X273" s="11"/>
-    </row>
-    <row r="274" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R273" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z273" s="11"/>
+    </row>
+    <row r="274" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
         <v>285</v>
       </c>
@@ -7672,12 +8978,12 @@
       <c r="E274" s="3">
         <v>4411171336</v>
       </c>
-      <c r="P274" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X274" s="11"/>
-    </row>
-    <row r="275" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R274" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z274" s="11"/>
+    </row>
+    <row r="275" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
         <v>286</v>
       </c>
@@ -7693,12 +8999,12 @@
       <c r="E275" s="3">
         <v>4724101883</v>
       </c>
-      <c r="P275" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X275" s="11"/>
-    </row>
-    <row r="276" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R275" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z275" s="11"/>
+    </row>
+    <row r="276" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
         <v>287</v>
       </c>
@@ -7708,12 +9014,12 @@
       <c r="C276" s="3">
         <v>3795496938</v>
       </c>
-      <c r="P276" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X276" s="11"/>
-    </row>
-    <row r="277" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R276" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z276" s="11"/>
+    </row>
+    <row r="277" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
         <v>288</v>
       </c>
@@ -7726,12 +9032,12 @@
       <c r="D277" s="3">
         <v>4411168663</v>
       </c>
-      <c r="P277" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X277" s="11"/>
-    </row>
-    <row r="278" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R277" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z277" s="11"/>
+    </row>
+    <row r="278" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
         <v>289</v>
       </c>
@@ -7741,12 +9047,12 @@
       <c r="C278" s="3">
         <v>3795498152</v>
       </c>
-      <c r="P278" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X278" s="11"/>
-    </row>
-    <row r="279" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R278" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z278" s="11"/>
+    </row>
+    <row r="279" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
         <v>290</v>
       </c>
@@ -7756,12 +9062,12 @@
       <c r="C279" s="3">
         <v>3795498549</v>
       </c>
-      <c r="P279" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X279" s="11"/>
-    </row>
-    <row r="280" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R279" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z279" s="11"/>
+    </row>
+    <row r="280" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
         <v>291</v>
       </c>
@@ -7774,12 +9080,12 @@
       <c r="D280" s="3">
         <v>4411169151</v>
       </c>
-      <c r="P280" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X280" s="11"/>
-    </row>
-    <row r="281" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R280" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z280" s="11"/>
+    </row>
+    <row r="281" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="4" t="s">
         <v>292</v>
       </c>
@@ -7792,12 +9098,12 @@
       <c r="D281" s="3">
         <v>4411168817</v>
       </c>
-      <c r="P281" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X281" s="11"/>
-    </row>
-    <row r="282" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R281" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z281" s="11"/>
+    </row>
+    <row r="282" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
         <v>293</v>
       </c>
@@ -7810,12 +9116,12 @@
       <c r="D282" s="3">
         <v>4411163071</v>
       </c>
-      <c r="P282" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X282" s="11"/>
-    </row>
-    <row r="283" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R282" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z282" s="11"/>
+    </row>
+    <row r="283" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
         <v>294</v>
       </c>
@@ -7828,12 +9134,12 @@
       <c r="D283" s="3">
         <v>4411169425</v>
       </c>
-      <c r="P283" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X283" s="11"/>
-    </row>
-    <row r="284" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R283" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z283" s="11"/>
+    </row>
+    <row r="284" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
         <v>295</v>
       </c>
@@ -7846,12 +9152,12 @@
       <c r="D284" s="3">
         <v>4411169080</v>
       </c>
-      <c r="P284" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X284" s="11"/>
-    </row>
-    <row r="285" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R284" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z284" s="11"/>
+    </row>
+    <row r="285" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
         <v>296</v>
       </c>
@@ -7864,12 +9170,12 @@
       <c r="D285" s="3">
         <v>4411167390</v>
       </c>
-      <c r="P285" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X285" s="11"/>
-    </row>
-    <row r="286" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R285" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z285" s="11"/>
+    </row>
+    <row r="286" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
         <v>297</v>
       </c>
@@ -7882,12 +9188,12 @@
       <c r="D286" s="3">
         <v>4411163514</v>
       </c>
-      <c r="P286" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X286" s="11"/>
-    </row>
-    <row r="287" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R286" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z286" s="11"/>
+    </row>
+    <row r="287" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="13" t="s">
         <v>298</v>
       </c>
@@ -7906,12 +9212,12 @@
       <c r="F287" s="3">
         <v>4443059125</v>
       </c>
-      <c r="P287" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="X287" s="11"/>
-    </row>
-    <row r="288" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R287" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z287" s="11"/>
+    </row>
+    <row r="288" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
         <v>299</v>
       </c>
@@ -7921,12 +9227,12 @@
       <c r="C288" s="3">
         <v>4410795843</v>
       </c>
-      <c r="P288" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X288" s="11"/>
-    </row>
-    <row r="289" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R288" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z288" s="11"/>
+    </row>
+    <row r="289" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
         <v>300</v>
       </c>
@@ -7936,12 +9242,12 @@
       <c r="C289" s="3">
         <v>4410792899</v>
       </c>
-      <c r="P289" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X289" s="11"/>
-    </row>
-    <row r="290" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R289" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z289" s="11"/>
+    </row>
+    <row r="290" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
         <v>301</v>
       </c>
@@ -7951,12 +9257,12 @@
       <c r="C290" s="3">
         <v>4410794178</v>
       </c>
-      <c r="P290" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X290" s="11"/>
-    </row>
-    <row r="291" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R290" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z290" s="11"/>
+    </row>
+    <row r="291" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="4" t="s">
         <v>302</v>
       </c>
@@ -7966,24 +9272,24 @@
       <c r="C291" s="3">
         <v>4410794548</v>
       </c>
-      <c r="P291" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X291" s="11"/>
-    </row>
-    <row r="292" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R291" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z291" s="11"/>
+    </row>
+    <row r="292" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
         <v>303</v>
       </c>
       <c r="B292" s="15">
         <v>2474252885</v>
       </c>
-      <c r="P292" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X292" s="11"/>
-    </row>
-    <row r="293" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R292" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z292" s="11"/>
+    </row>
+    <row r="293" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
         <v>304</v>
       </c>
@@ -7993,12 +9299,12 @@
       <c r="C293" s="3">
         <v>4410795061</v>
       </c>
-      <c r="P293" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X293" s="11"/>
-    </row>
-    <row r="294" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R293" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z293" s="11"/>
+    </row>
+    <row r="294" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
         <v>305</v>
       </c>
@@ -8008,12 +9314,12 @@
       <c r="C294" s="5">
         <v>4410794283</v>
       </c>
-      <c r="P294" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X294" s="11"/>
-    </row>
-    <row r="295" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R294" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z294" s="11"/>
+    </row>
+    <row r="295" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
         <v>306</v>
       </c>
@@ -8023,12 +9329,12 @@
       <c r="C295" s="3">
         <v>4410793109</v>
       </c>
-      <c r="P295" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X295" s="11"/>
-    </row>
-    <row r="296" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R295" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z295" s="11"/>
+    </row>
+    <row r="296" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
         <v>307</v>
       </c>
@@ -8038,36 +9344,36 @@
       <c r="C296" s="3">
         <v>4410794696</v>
       </c>
-      <c r="P296" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X296" s="11"/>
-    </row>
-    <row r="297" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R296" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z296" s="11"/>
+    </row>
+    <row r="297" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
         <v>308</v>
       </c>
       <c r="B297" s="15">
         <v>2474254390</v>
       </c>
-      <c r="P297" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X297" s="11"/>
-    </row>
-    <row r="298" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R297" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z297" s="11"/>
+    </row>
+    <row r="298" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
         <v>309</v>
       </c>
       <c r="B298" s="15">
         <v>2474254998</v>
       </c>
-      <c r="P298" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X298" s="11"/>
-    </row>
-    <row r="299" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R298" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z298" s="11"/>
+    </row>
+    <row r="299" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
         <v>310</v>
       </c>
@@ -8077,72 +9383,72 @@
       <c r="C299" s="3">
         <v>4410796092</v>
       </c>
-      <c r="P299" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X299" s="11"/>
-    </row>
-    <row r="300" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R299" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z299" s="11"/>
+    </row>
+    <row r="300" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
         <v>311</v>
       </c>
       <c r="B300" s="15">
         <v>2474251925</v>
       </c>
-      <c r="P300" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X300" s="11"/>
-    </row>
-    <row r="301" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R300" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z300" s="11"/>
+    </row>
+    <row r="301" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
         <v>312</v>
       </c>
       <c r="B301" s="15">
         <v>2474254255</v>
       </c>
-      <c r="P301" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X301" s="11"/>
-    </row>
-    <row r="302" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R301" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z301" s="11"/>
+    </row>
+    <row r="302" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
         <v>313</v>
       </c>
       <c r="B302" s="15">
         <v>2474254585</v>
       </c>
-      <c r="P302" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X302" s="11"/>
-    </row>
-    <row r="303" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R302" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z302" s="11"/>
+    </row>
+    <row r="303" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
         <v>314</v>
       </c>
       <c r="B303" s="15">
         <v>2474252626</v>
       </c>
-      <c r="P303" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X303" s="11"/>
-    </row>
-    <row r="304" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R303" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z303" s="11"/>
+    </row>
+    <row r="304" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
         <v>315</v>
       </c>
       <c r="B304" s="15">
         <v>2474251481</v>
       </c>
-      <c r="P304" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X304" s="11"/>
-    </row>
-    <row r="305" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R304" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z304" s="11"/>
+    </row>
+    <row r="305" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
         <v>316</v>
       </c>
@@ -8152,12 +9458,12 @@
       <c r="C305" s="5">
         <v>4410793689</v>
       </c>
-      <c r="P305" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X305" s="11"/>
-    </row>
-    <row r="306" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R305" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z305" s="11"/>
+    </row>
+    <row r="306" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
         <v>317</v>
       </c>
@@ -8167,12 +9473,12 @@
       <c r="C306" s="3">
         <v>4410793826</v>
       </c>
-      <c r="P306" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X306" s="11"/>
-    </row>
-    <row r="307" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R306" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z306" s="11"/>
+    </row>
+    <row r="307" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4" t="s">
         <v>318</v>
       </c>
@@ -8182,12 +9488,12 @@
       <c r="C307" s="3">
         <v>4410794361</v>
       </c>
-      <c r="P307" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X307" s="11"/>
-    </row>
-    <row r="308" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R307" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z307" s="11"/>
+    </row>
+    <row r="308" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
         <v>319</v>
       </c>
@@ -8197,12 +9503,12 @@
       <c r="C308" s="3">
         <v>4410793497</v>
       </c>
-      <c r="P308" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X308" s="11"/>
-    </row>
-    <row r="309" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R308" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z308" s="11"/>
+    </row>
+    <row r="309" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4" t="s">
         <v>320</v>
       </c>
@@ -8212,12 +9518,12 @@
       <c r="C309" s="3">
         <v>4410794492</v>
       </c>
-      <c r="P309" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X309" s="11"/>
-    </row>
-    <row r="310" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R309" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z309" s="11"/>
+    </row>
+    <row r="310" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4" t="s">
         <v>321</v>
       </c>
@@ -8227,36 +9533,36 @@
       <c r="C310" s="3">
         <v>4410794643</v>
       </c>
-      <c r="P310" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X310" s="11"/>
-    </row>
-    <row r="311" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R310" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z310" s="11"/>
+    </row>
+    <row r="311" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4" t="s">
         <v>322</v>
       </c>
       <c r="B311" s="15">
         <v>2474253325</v>
       </c>
-      <c r="P311" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X311" s="11"/>
-    </row>
-    <row r="312" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R311" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z311" s="11"/>
+    </row>
+    <row r="312" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
         <v>323</v>
       </c>
       <c r="B312" s="15">
         <v>2474253882</v>
       </c>
-      <c r="P312" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X312" s="11"/>
-    </row>
-    <row r="313" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R312" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z312" s="11"/>
+    </row>
+    <row r="313" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4" t="s">
         <v>324</v>
       </c>
@@ -8266,12 +9572,12 @@
       <c r="C313" s="3">
         <v>4410793924</v>
       </c>
-      <c r="P313" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X313" s="11"/>
-    </row>
-    <row r="314" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R313" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z313" s="11"/>
+    </row>
+    <row r="314" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4" t="s">
         <v>325</v>
       </c>
@@ -8281,12 +9587,12 @@
       <c r="C314" s="3">
         <v>4352308658</v>
       </c>
-      <c r="P314" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X314" s="11"/>
-    </row>
-    <row r="315" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R314" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z314" s="11"/>
+    </row>
+    <row r="315" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="4" t="s">
         <v>326</v>
       </c>
@@ -8296,24 +9602,24 @@
       <c r="C315" s="3">
         <v>4410793050</v>
       </c>
-      <c r="P315" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X315" s="11"/>
-    </row>
-    <row r="316" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R315" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z315" s="11"/>
+    </row>
+    <row r="316" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
         <v>327</v>
       </c>
       <c r="B316" s="15">
         <v>2474431127</v>
       </c>
-      <c r="P316" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X316" s="11"/>
-    </row>
-    <row r="317" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R316" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z316" s="11"/>
+    </row>
+    <row r="317" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
         <v>328</v>
       </c>
@@ -8326,12 +9632,12 @@
       <c r="D317" s="3">
         <v>4086257096</v>
       </c>
-      <c r="P317" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X317" s="11"/>
-    </row>
-    <row r="318" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R317" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z317" s="11"/>
+    </row>
+    <row r="318" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
         <v>329</v>
       </c>
@@ -8341,12 +9647,12 @@
       <c r="C318" s="3">
         <v>4544759914</v>
       </c>
-      <c r="P318" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X318" s="11"/>
-    </row>
-    <row r="319" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R318" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z318" s="11"/>
+    </row>
+    <row r="319" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
         <v>330</v>
       </c>
@@ -8356,12 +9662,12 @@
       <c r="C319" s="3">
         <v>4544759944</v>
       </c>
-      <c r="P319" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X319" s="11"/>
-    </row>
-    <row r="320" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R319" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z319" s="11"/>
+    </row>
+    <row r="320" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
         <v>331</v>
       </c>
@@ -8374,12 +9680,12 @@
       <c r="D320" s="3">
         <v>4086258895</v>
       </c>
-      <c r="P320" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X320" s="11"/>
-    </row>
-    <row r="321" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R320" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z320" s="11"/>
+    </row>
+    <row r="321" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
         <v>332</v>
       </c>
@@ -8392,12 +9698,12 @@
       <c r="D321" s="3">
         <v>4086257286</v>
       </c>
-      <c r="P321" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X321" s="11"/>
-    </row>
-    <row r="322" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R321" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z321" s="11"/>
+    </row>
+    <row r="322" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
         <v>333</v>
       </c>
@@ -8410,12 +9716,12 @@
       <c r="D322" s="3">
         <v>4086260262</v>
       </c>
-      <c r="P322" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X322" s="11"/>
-    </row>
-    <row r="323" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R322" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z322" s="11"/>
+    </row>
+    <row r="323" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
         <v>334</v>
       </c>
@@ -8428,24 +9734,24 @@
       <c r="D323" s="3">
         <v>4086264776</v>
       </c>
-      <c r="P323" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X323" s="11"/>
-    </row>
-    <row r="324" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R323" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z323" s="11"/>
+    </row>
+    <row r="324" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
         <v>335</v>
       </c>
       <c r="B324" s="15">
         <v>3691843469</v>
       </c>
-      <c r="P324" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X324" s="11"/>
-    </row>
-    <row r="325" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R324" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z324" s="11"/>
+    </row>
+    <row r="325" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
         <v>336</v>
       </c>
@@ -8458,24 +9764,24 @@
       <c r="D325" s="3">
         <v>4086265043</v>
       </c>
-      <c r="P325" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X325" s="11"/>
-    </row>
-    <row r="326" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R325" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z325" s="11"/>
+    </row>
+    <row r="326" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
         <v>337</v>
       </c>
       <c r="B326" s="15">
         <v>3691843790</v>
       </c>
-      <c r="P326" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X326" s="11"/>
-    </row>
-    <row r="327" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R326" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z326" s="11"/>
+    </row>
+    <row r="327" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
         <v>338</v>
       </c>
@@ -8488,12 +9794,12 @@
       <c r="D327" s="3">
         <v>4086265237</v>
       </c>
-      <c r="P327" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X327" s="11"/>
-    </row>
-    <row r="328" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R327" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z327" s="11"/>
+    </row>
+    <row r="328" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="4" t="s">
         <v>339</v>
       </c>
@@ -8503,12 +9809,12 @@
       <c r="C328" s="3">
         <v>4544761808</v>
       </c>
-      <c r="P328" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X328" s="11"/>
-    </row>
-    <row r="329" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R328" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z328" s="11"/>
+    </row>
+    <row r="329" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="4" t="s">
         <v>340</v>
       </c>
@@ -8521,12 +9827,12 @@
       <c r="D329" s="3">
         <v>4086264435</v>
       </c>
-      <c r="P329" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X329" s="11"/>
-    </row>
-    <row r="330" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R329" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z329" s="11"/>
+    </row>
+    <row r="330" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
         <v>341</v>
       </c>
@@ -8539,12 +9845,12 @@
       <c r="D330" s="3">
         <v>4086268210</v>
       </c>
-      <c r="P330" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X330" s="11"/>
-    </row>
-    <row r="331" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R330" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z330" s="11"/>
+    </row>
+    <row r="331" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
         <v>342</v>
       </c>
@@ -8557,12 +9863,12 @@
       <c r="D331" s="3">
         <v>4086269638</v>
       </c>
-      <c r="P331" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X331" s="11"/>
-    </row>
-    <row r="332" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R331" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z331" s="11"/>
+    </row>
+    <row r="332" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
         <v>343</v>
       </c>
@@ -8575,12 +9881,12 @@
       <c r="D332" s="3">
         <v>4086264553</v>
       </c>
-      <c r="P332" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X332" s="11"/>
-    </row>
-    <row r="333" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R332" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z332" s="11"/>
+    </row>
+    <row r="333" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
         <v>344</v>
       </c>
@@ -8593,12 +9899,12 @@
       <c r="D333" s="3">
         <v>4086264799</v>
       </c>
-      <c r="P333" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X333" s="11"/>
-    </row>
-    <row r="334" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R333" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z333" s="11"/>
+    </row>
+    <row r="334" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
         <v>345</v>
       </c>
@@ -8611,12 +9917,12 @@
       <c r="D334" s="3">
         <v>4086264238</v>
       </c>
-      <c r="P334" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X334" s="11"/>
-    </row>
-    <row r="335" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R334" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z334" s="11"/>
+    </row>
+    <row r="335" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="4" t="s">
         <v>346</v>
       </c>
@@ -8629,12 +9935,12 @@
       <c r="D335" s="3">
         <v>4086264520</v>
       </c>
-      <c r="P335" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X335" s="11"/>
-    </row>
-    <row r="336" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R335" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z335" s="11"/>
+    </row>
+    <row r="336" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
         <v>347</v>
       </c>
@@ -8647,12 +9953,12 @@
       <c r="D336" s="3">
         <v>4086258042</v>
       </c>
-      <c r="P336" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X336" s="11"/>
-    </row>
-    <row r="337" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R336" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z336" s="11"/>
+    </row>
+    <row r="337" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
         <v>348</v>
       </c>
@@ -8665,12 +9971,12 @@
       <c r="D337" s="3">
         <v>4086263550</v>
       </c>
-      <c r="P337" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X337" s="11"/>
-    </row>
-    <row r="338" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R337" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z337" s="11"/>
+    </row>
+    <row r="338" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
         <v>349</v>
       </c>
@@ -8683,12 +9989,12 @@
       <c r="D338" s="3">
         <v>4086263588</v>
       </c>
-      <c r="P338" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X338" s="11"/>
-    </row>
-    <row r="339" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R338" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z338" s="11"/>
+    </row>
+    <row r="339" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
         <v>350</v>
       </c>
@@ -8701,12 +10007,12 @@
       <c r="D339" s="3">
         <v>4086265051</v>
       </c>
-      <c r="P339" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X339" s="11"/>
-    </row>
-    <row r="340" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R339" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z339" s="11"/>
+    </row>
+    <row r="340" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
         <v>351</v>
       </c>
@@ -8719,12 +10025,12 @@
       <c r="D340" s="3">
         <v>4086263292</v>
       </c>
-      <c r="P340" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X340" s="11"/>
-    </row>
-    <row r="341" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R340" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z340" s="11"/>
+    </row>
+    <row r="341" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
         <v>352</v>
       </c>
@@ -8737,12 +10043,12 @@
       <c r="D341" s="3">
         <v>4086263416</v>
       </c>
-      <c r="P341" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X341" s="11"/>
-    </row>
-    <row r="342" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R341" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z341" s="11"/>
+    </row>
+    <row r="342" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
         <v>353</v>
       </c>
@@ -8755,12 +10061,12 @@
       <c r="D342" s="3">
         <v>4086258692</v>
       </c>
-      <c r="P342" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X342" s="11"/>
-    </row>
-    <row r="343" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R342" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z342" s="11"/>
+    </row>
+    <row r="343" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
         <v>354</v>
       </c>
@@ -8773,12 +10079,12 @@
       <c r="D343" s="3">
         <v>4086263152</v>
       </c>
-      <c r="P343" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X343" s="11"/>
-    </row>
-    <row r="344" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R343" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z343" s="11"/>
+    </row>
+    <row r="344" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="4" t="s">
         <v>355</v>
       </c>
@@ -8791,12 +10097,12 @@
       <c r="D344" s="3">
         <v>4086266623</v>
       </c>
-      <c r="P344" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X344" s="11"/>
-    </row>
-    <row r="345" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R344" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z344" s="11"/>
+    </row>
+    <row r="345" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="4" t="s">
         <v>356</v>
       </c>
@@ -8809,12 +10115,12 @@
       <c r="D345" s="3">
         <v>4086260019</v>
       </c>
-      <c r="P345" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X345" s="11"/>
-    </row>
-    <row r="346" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R345" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z345" s="11"/>
+    </row>
+    <row r="346" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="4" t="s">
         <v>357</v>
       </c>
@@ -8827,12 +10133,12 @@
       <c r="D346" s="3">
         <v>4431489467</v>
       </c>
-      <c r="P346" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X346" s="11"/>
-    </row>
-    <row r="347" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R346" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z346" s="11"/>
+    </row>
+    <row r="347" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="4" t="s">
         <v>358</v>
       </c>
@@ -8842,12 +10148,12 @@
       <c r="C347" s="3">
         <v>4544768974</v>
       </c>
-      <c r="P347" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X347" s="11"/>
-    </row>
-    <row r="348" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R347" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z347" s="11"/>
+    </row>
+    <row r="348" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="4" t="s">
         <v>359</v>
       </c>
@@ -8860,12 +10166,12 @@
       <c r="D348" s="3">
         <v>4086264493</v>
       </c>
-      <c r="P348" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X348" s="11"/>
-    </row>
-    <row r="349" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R348" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z348" s="11"/>
+    </row>
+    <row r="349" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="4" t="s">
         <v>360</v>
       </c>
@@ -8875,12 +10181,12 @@
       <c r="C349" s="3">
         <v>4544751038</v>
       </c>
-      <c r="P349" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X349" s="11"/>
-    </row>
-    <row r="350" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R349" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z349" s="11"/>
+    </row>
+    <row r="350" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="4" t="s">
         <v>361</v>
       </c>
@@ -8893,12 +10199,12 @@
       <c r="D350" s="3">
         <v>4086258905</v>
       </c>
-      <c r="P350" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X350" s="11"/>
-    </row>
-    <row r="351" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R350" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z350" s="11"/>
+    </row>
+    <row r="351" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="4" t="s">
         <v>362</v>
       </c>
@@ -8911,12 +10217,12 @@
       <c r="D351" s="3">
         <v>4086265396</v>
       </c>
-      <c r="P351" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X351" s="11"/>
-    </row>
-    <row r="352" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R351" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z351" s="11"/>
+    </row>
+    <row r="352" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="4" t="s">
         <v>363</v>
       </c>
@@ -8929,12 +10235,12 @@
       <c r="D352" s="3">
         <v>4086263559</v>
       </c>
-      <c r="P352" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X352" s="11"/>
-    </row>
-    <row r="353" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R352" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z352" s="11"/>
+    </row>
+    <row r="353" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="4" t="s">
         <v>364</v>
       </c>
@@ -8947,12 +10253,12 @@
       <c r="D353" s="3">
         <v>4086263717</v>
       </c>
-      <c r="P353" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X353" s="11"/>
-    </row>
-    <row r="354" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R353" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z353" s="11"/>
+    </row>
+    <row r="354" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="4" t="s">
         <v>365</v>
       </c>
@@ -8965,12 +10271,12 @@
       <c r="D354" s="3">
         <v>4086266543</v>
       </c>
-      <c r="P354" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X354" s="11"/>
-    </row>
-    <row r="355" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R354" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z354" s="11"/>
+    </row>
+    <row r="355" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="4" t="s">
         <v>366</v>
       </c>
@@ -8983,12 +10289,12 @@
       <c r="D355" s="3">
         <v>4086258058</v>
       </c>
-      <c r="P355" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X355" s="11"/>
-    </row>
-    <row r="356" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R355" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z355" s="11"/>
+    </row>
+    <row r="356" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="4" t="s">
         <v>367</v>
       </c>
@@ -9001,12 +10307,12 @@
       <c r="D356" s="3">
         <v>4086268182</v>
       </c>
-      <c r="P356" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X356" s="11"/>
-    </row>
-    <row r="357" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R356" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z356" s="11"/>
+    </row>
+    <row r="357" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="4" t="s">
         <v>368</v>
       </c>
@@ -9016,12 +10322,12 @@
       <c r="C357" s="3">
         <v>4544771182</v>
       </c>
-      <c r="P357" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X357" s="11"/>
-    </row>
-    <row r="358" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R357" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z357" s="11"/>
+    </row>
+    <row r="358" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="4" t="s">
         <v>369</v>
       </c>
@@ -9034,24 +10340,24 @@
       <c r="D358" s="3">
         <v>4086258252</v>
       </c>
-      <c r="P358" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X358" s="11"/>
-    </row>
-    <row r="359" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R358" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z358" s="11"/>
+    </row>
+    <row r="359" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="4" t="s">
         <v>370</v>
       </c>
       <c r="B359" s="15">
         <v>3697385469</v>
       </c>
-      <c r="P359" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X359" s="11"/>
-    </row>
-    <row r="360" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R359" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z359" s="11"/>
+    </row>
+    <row r="360" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="4" t="s">
         <v>371</v>
       </c>
@@ -9064,12 +10370,12 @@
       <c r="D360" s="3">
         <v>4086259075</v>
       </c>
-      <c r="P360" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X360" s="11"/>
-    </row>
-    <row r="361" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R360" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z360" s="11"/>
+    </row>
+    <row r="361" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="4" t="s">
         <v>372</v>
       </c>
@@ -9082,12 +10388,12 @@
       <c r="D361" s="3">
         <v>4086264413</v>
       </c>
-      <c r="P361" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X361" s="11"/>
-    </row>
-    <row r="362" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R361" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z361" s="11"/>
+    </row>
+    <row r="362" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="4" t="s">
         <v>373</v>
       </c>
@@ -9097,12 +10403,12 @@
       <c r="C362" s="3">
         <v>4544765611</v>
       </c>
-      <c r="P362" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X362" s="11"/>
-    </row>
-    <row r="363" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R362" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z362" s="11"/>
+    </row>
+    <row r="363" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="4" t="s">
         <v>374</v>
       </c>
@@ -9115,12 +10421,12 @@
       <c r="D363" s="3">
         <v>4086258395</v>
       </c>
-      <c r="P363" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X363" s="11"/>
-    </row>
-    <row r="364" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R363" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z363" s="11"/>
+    </row>
+    <row r="364" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="4" t="s">
         <v>375</v>
       </c>
@@ -9133,12 +10439,12 @@
       <c r="D364" s="3">
         <v>4086258367</v>
       </c>
-      <c r="P364" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X364" s="11"/>
-    </row>
-    <row r="365" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R364" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z364" s="11"/>
+    </row>
+    <row r="365" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="4" t="s">
         <v>376</v>
       </c>
@@ -9151,12 +10457,12 @@
       <c r="D365" s="3">
         <v>4086263561</v>
       </c>
-      <c r="P365" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X365" s="11"/>
-    </row>
-    <row r="366" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R365" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z365" s="11"/>
+    </row>
+    <row r="366" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="4" t="s">
         <v>377</v>
       </c>
@@ -9169,12 +10475,12 @@
       <c r="D366" s="3">
         <v>4086268091</v>
       </c>
-      <c r="P366" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X366" s="11"/>
-    </row>
-    <row r="367" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R366" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z366" s="11"/>
+    </row>
+    <row r="367" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="4" t="s">
         <v>378</v>
       </c>
@@ -9187,12 +10493,12 @@
       <c r="D367" s="3">
         <v>4086269800</v>
       </c>
-      <c r="P367" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X367" s="11"/>
-    </row>
-    <row r="368" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R367" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z367" s="11"/>
+    </row>
+    <row r="368" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="4" t="s">
         <v>379</v>
       </c>
@@ -9205,12 +10511,12 @@
       <c r="D368" s="3">
         <v>4086263881</v>
       </c>
-      <c r="P368" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X368" s="11"/>
-    </row>
-    <row r="369" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R368" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z368" s="11"/>
+    </row>
+    <row r="369" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="4" t="s">
         <v>380</v>
       </c>
@@ -9223,12 +10529,12 @@
       <c r="D369" s="3">
         <v>4086270302</v>
       </c>
-      <c r="P369" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X369" s="11"/>
-    </row>
-    <row r="370" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R369" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z369" s="11"/>
+    </row>
+    <row r="370" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="4" t="s">
         <v>381</v>
       </c>
@@ -9238,12 +10544,12 @@
       <c r="C370" s="3">
         <v>4544772762</v>
       </c>
-      <c r="P370" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X370" s="11"/>
-    </row>
-    <row r="371" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R370" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z370" s="11"/>
+    </row>
+    <row r="371" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="4" t="s">
         <v>382</v>
       </c>
@@ -9256,12 +10562,12 @@
       <c r="D371" s="3">
         <v>4086264843</v>
       </c>
-      <c r="P371" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X371" s="11"/>
-    </row>
-    <row r="372" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R371" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z371" s="11"/>
+    </row>
+    <row r="372" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="4" t="s">
         <v>383</v>
       </c>
@@ -9274,12 +10580,12 @@
       <c r="D372" s="3">
         <v>4086263739</v>
       </c>
-      <c r="P372" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X372" s="11"/>
-    </row>
-    <row r="373" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R372" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z372" s="11"/>
+    </row>
+    <row r="373" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="4" t="s">
         <v>384</v>
       </c>
@@ -9292,12 +10598,12 @@
       <c r="D373" s="3">
         <v>4086263993</v>
       </c>
-      <c r="P373" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X373" s="11"/>
-    </row>
-    <row r="374" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R373" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z373" s="11"/>
+    </row>
+    <row r="374" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="4" t="s">
         <v>385</v>
       </c>
@@ -9307,12 +10613,12 @@
       <c r="C374" s="3">
         <v>4544771769</v>
       </c>
-      <c r="P374" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X374" s="11"/>
-    </row>
-    <row r="375" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R374" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z374" s="11"/>
+    </row>
+    <row r="375" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="4" t="s">
         <v>386</v>
       </c>
@@ -9325,12 +10631,12 @@
       <c r="D375" s="3">
         <v>4086268414</v>
       </c>
-      <c r="P375" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X375" s="11"/>
-    </row>
-    <row r="376" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R375" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z375" s="11"/>
+    </row>
+    <row r="376" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="4" t="s">
         <v>387</v>
       </c>
@@ -9343,12 +10649,12 @@
       <c r="D376" s="3">
         <v>4086258111</v>
       </c>
-      <c r="P376" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X376" s="11"/>
-    </row>
-    <row r="377" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R376" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z376" s="11"/>
+    </row>
+    <row r="377" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="4" t="s">
         <v>388</v>
       </c>
@@ -9361,12 +10667,12 @@
       <c r="D377" s="3">
         <v>4086264061</v>
       </c>
-      <c r="P377" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X377" s="11"/>
-    </row>
-    <row r="378" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R377" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z377" s="11"/>
+    </row>
+    <row r="378" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="4" t="s">
         <v>389</v>
       </c>
@@ -9379,12 +10685,12 @@
       <c r="D378" s="3">
         <v>4086265130</v>
       </c>
-      <c r="P378" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X378" s="11"/>
-    </row>
-    <row r="379" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R378" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z378" s="11"/>
+    </row>
+    <row r="379" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="4" t="s">
         <v>390</v>
       </c>
@@ -9397,12 +10703,12 @@
       <c r="D379" s="3">
         <v>4086268682</v>
       </c>
-      <c r="P379" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X379" s="11"/>
-    </row>
-    <row r="380" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R379" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z379" s="11"/>
+    </row>
+    <row r="380" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="4" t="s">
         <v>391</v>
       </c>
@@ -9415,12 +10721,12 @@
       <c r="D380" s="3">
         <v>4086257798</v>
       </c>
-      <c r="P380" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X380" s="11"/>
-    </row>
-    <row r="381" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R380" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z380" s="11"/>
+    </row>
+    <row r="381" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="4" t="s">
         <v>392</v>
       </c>
@@ -9433,12 +10739,12 @@
       <c r="D381" s="3">
         <v>4086265449</v>
       </c>
-      <c r="P381" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X381" s="11"/>
-    </row>
-    <row r="382" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R381" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z381" s="11"/>
+    </row>
+    <row r="382" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="4" t="s">
         <v>393</v>
       </c>
@@ -9448,12 +10754,12 @@
       <c r="C382" s="3">
         <v>4544759886</v>
       </c>
-      <c r="P382" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X382" s="11"/>
-    </row>
-    <row r="383" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R382" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z382" s="11"/>
+    </row>
+    <row r="383" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="4" t="s">
         <v>394</v>
       </c>
@@ -9466,12 +10772,12 @@
       <c r="D383" s="3">
         <v>4086267459</v>
       </c>
-      <c r="P383" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X383" s="11"/>
-    </row>
-    <row r="384" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R383" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z383" s="11"/>
+    </row>
+    <row r="384" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="4" t="s">
         <v>395</v>
       </c>
@@ -9484,12 +10790,12 @@
       <c r="D384" s="3">
         <v>4086266739</v>
       </c>
-      <c r="P384" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X384" s="11"/>
-    </row>
-    <row r="385" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R384" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z384" s="11"/>
+    </row>
+    <row r="385" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="4" t="s">
         <v>396</v>
       </c>
@@ -9499,12 +10805,12 @@
       <c r="C385" s="3">
         <v>4544790815</v>
       </c>
-      <c r="P385" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X385" s="11"/>
-    </row>
-    <row r="386" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R385" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z385" s="11"/>
+    </row>
+    <row r="386" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="4" t="s">
         <v>397</v>
       </c>
@@ -9514,12 +10820,12 @@
       <c r="C386" s="3">
         <v>4544759610</v>
       </c>
-      <c r="P386" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X386" s="11"/>
-    </row>
-    <row r="387" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R386" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z386" s="11"/>
+    </row>
+    <row r="387" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="4" t="s">
         <v>398</v>
       </c>
@@ -9532,12 +10838,12 @@
       <c r="D387" s="3">
         <v>4086265504</v>
       </c>
-      <c r="P387" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X387" s="11"/>
-    </row>
-    <row r="388" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R387" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z387" s="11"/>
+    </row>
+    <row r="388" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="4" t="s">
         <v>399</v>
       </c>
@@ -9550,12 +10856,12 @@
       <c r="D388" s="3">
         <v>4086265129</v>
       </c>
-      <c r="P388" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X388" s="11"/>
-    </row>
-    <row r="389" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R388" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z388" s="11"/>
+    </row>
+    <row r="389" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="4" t="s">
         <v>400</v>
       </c>
@@ -9568,12 +10874,12 @@
       <c r="D389" s="3">
         <v>4086263860</v>
       </c>
-      <c r="P389" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X389" s="11"/>
-    </row>
-    <row r="390" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R389" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z389" s="11"/>
+    </row>
+    <row r="390" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="4" t="s">
         <v>401</v>
       </c>
@@ -9583,12 +10889,12 @@
       <c r="C390" s="5">
         <v>4544762172</v>
       </c>
-      <c r="P390" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X390" s="11"/>
-    </row>
-    <row r="391" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R390" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z390" s="11"/>
+    </row>
+    <row r="391" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="4" t="s">
         <v>402</v>
       </c>
@@ -9598,12 +10904,12 @@
       <c r="C391" s="3">
         <v>4544769643</v>
       </c>
-      <c r="P391" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X391" s="11"/>
-    </row>
-    <row r="392" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R391" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z391" s="11"/>
+    </row>
+    <row r="392" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="4" t="s">
         <v>403</v>
       </c>
@@ -9616,12 +10922,12 @@
       <c r="D392" s="3">
         <v>4086258729</v>
       </c>
-      <c r="P392" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X392" s="11"/>
-    </row>
-    <row r="393" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R392" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z392" s="11"/>
+    </row>
+    <row r="393" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="4" t="s">
         <v>404</v>
       </c>
@@ -9634,12 +10940,12 @@
       <c r="D393" s="3">
         <v>4086263587</v>
       </c>
-      <c r="P393" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X393" s="11"/>
-    </row>
-    <row r="394" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R393" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z393" s="11"/>
+    </row>
+    <row r="394" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="4" t="s">
         <v>405</v>
       </c>
@@ -9652,12 +10958,12 @@
       <c r="D394" s="3">
         <v>4086258113</v>
       </c>
-      <c r="P394" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X394" s="11"/>
-    </row>
-    <row r="395" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R394" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z394" s="11"/>
+    </row>
+    <row r="395" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="4" t="s">
         <v>406</v>
       </c>
@@ -9670,12 +10976,12 @@
       <c r="D395" s="3">
         <v>4086264485</v>
       </c>
-      <c r="P395" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X395" s="11"/>
-    </row>
-    <row r="396" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R395" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z395" s="11"/>
+    </row>
+    <row r="396" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="4" t="s">
         <v>407</v>
       </c>
@@ -9688,12 +10994,12 @@
       <c r="D396" s="3">
         <v>4086258409</v>
       </c>
-      <c r="P396" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X396" s="11"/>
-    </row>
-    <row r="397" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R396" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z396" s="11"/>
+    </row>
+    <row r="397" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="4" t="s">
         <v>408</v>
       </c>
@@ -9706,12 +11012,12 @@
       <c r="D397" s="3">
         <v>4086257806</v>
       </c>
-      <c r="P397" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X397" s="11"/>
-    </row>
-    <row r="398" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R397" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z397" s="11"/>
+    </row>
+    <row r="398" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="4" t="s">
         <v>409</v>
       </c>
@@ -9724,12 +11030,12 @@
       <c r="D398" s="3">
         <v>4086260890</v>
       </c>
-      <c r="P398" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X398" s="11"/>
-    </row>
-    <row r="399" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R398" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z398" s="11"/>
+    </row>
+    <row r="399" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="4" t="s">
         <v>410</v>
       </c>
@@ -9742,12 +11048,12 @@
       <c r="D399" s="3">
         <v>4086258137</v>
       </c>
-      <c r="P399" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X399" s="11"/>
-    </row>
-    <row r="400" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R399" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z399" s="11"/>
+    </row>
+    <row r="400" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="4" t="s">
         <v>411</v>
       </c>
@@ -9760,12 +11066,12 @@
       <c r="D400" s="3">
         <v>4086258803</v>
       </c>
-      <c r="P400" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X400" s="11"/>
-    </row>
-    <row r="401" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R400" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z400" s="11"/>
+    </row>
+    <row r="401" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="4" t="s">
         <v>412</v>
       </c>
@@ -9778,12 +11084,12 @@
       <c r="D401" s="3">
         <v>4086259664</v>
       </c>
-      <c r="P401" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X401" s="11"/>
-    </row>
-    <row r="402" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R401" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z401" s="11"/>
+    </row>
+    <row r="402" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="4" t="s">
         <v>413</v>
       </c>
@@ -9793,12 +11099,12 @@
       <c r="C402" s="3">
         <v>4086258183</v>
       </c>
-      <c r="P402" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X402" s="11"/>
-    </row>
-    <row r="403" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R402" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z402" s="11"/>
+    </row>
+    <row r="403" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="4" t="s">
         <v>414</v>
       </c>
@@ -9808,12 +11114,12 @@
       <c r="C403" s="3">
         <v>4544764731</v>
       </c>
-      <c r="P403" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X403" s="11"/>
-    </row>
-    <row r="404" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R403" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z403" s="11"/>
+    </row>
+    <row r="404" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="4" t="s">
         <v>415</v>
       </c>
@@ -9823,23 +11129,23 @@
       <c r="C404" s="3">
         <v>4544763258</v>
       </c>
-      <c r="P404" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="X404" s="11"/>
-    </row>
-    <row r="405" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="R404" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z404" s="11"/>
+    </row>
+    <row r="405" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C405" s="6"/>
       <c r="D405" s="6"/>
       <c r="E405" s="6"/>
     </row>
-    <row r="406" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C406" s="6"/>
     </row>
-    <row r="407" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C407" s="6"/>
     </row>
-    <row r="408" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C408" s="6"/>
     </row>
   </sheetData>
